--- a/p_gps_pts1_groupno.xlsx
+++ b/p_gps_pts1_groupno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E27E93FE-057A-433C-80E8-4BF8A3DA57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{E27E93FE-057A-433C-80E8-4BF8A3DA57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F935D0A7-7E34-4E18-A911-5DCEEEBA1BB3}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="150" windowWidth="28320" windowHeight="15315" xr2:uid="{05EB62A8-AD25-4BA7-B277-61FA4B199BDB}"/>
+    <workbookView xWindow="480" yWindow="45" windowWidth="28320" windowHeight="15315" xr2:uid="{05EB62A8-AD25-4BA7-B277-61FA4B199BDB}"/>
   </bookViews>
   <sheets>
     <sheet name="p_gps_pts1_groupno" sheetId="1" r:id="rId1"/>
@@ -2147,7 +2147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2278,6 +2278,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2657,9 +2665,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3036,138 +3044,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B52F13-8966-47C6-8960-2C41BC3E18EA}">
   <dimension ref="A1:AF289"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="5" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="225.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="17.7109375" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.85546875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="22.7109375" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="16.28515625" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="24.5703125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="21.7109375" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" hidden="1" customWidth="1"/>
-    <col min="27" max="27" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="29.85546875" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="19" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.5703125" customWidth="1"/>
+    <col min="21" max="21" width="23.5703125" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" customWidth="1"/>
+    <col min="23" max="23" width="17" customWidth="1"/>
+    <col min="24" max="24" width="26.5703125" customWidth="1"/>
+    <col min="25" max="25" width="22.28515625" customWidth="1"/>
+    <col min="26" max="26" width="15.28515625" customWidth="1"/>
+    <col min="27" max="27" width="22.42578125" customWidth="1"/>
+    <col min="28" max="28" width="31.140625" customWidth="1"/>
     <col min="29" max="29" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="255.7109375" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="255.7109375" customWidth="1"/>
     <col min="31" max="31" width="36" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:32" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AE1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AF1" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3265,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3363,7 +3371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3461,7 +3469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3559,7 +3567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3657,7 +3665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3755,7 +3763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3853,7 +3861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3951,7 +3959,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4049,7 +4057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4147,7 +4155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4245,7 +4253,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4343,7 +4351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4441,7 +4449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4539,7 +4547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4637,7 +4645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4735,7 +4743,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4833,7 +4841,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4931,7 +4939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5029,7 +5037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5127,7 +5135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5225,7 +5233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5323,7 +5331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5421,7 +5429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5519,7 +5527,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5617,7 +5625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5715,7 +5723,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5813,7 +5821,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5911,7 +5919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6009,7 +6017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6107,7 +6115,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6205,7 +6213,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6303,7 +6311,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6401,7 +6409,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6499,7 +6507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6597,7 +6605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6695,7 +6703,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6793,7 +6801,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6891,7 +6899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6989,7 +6997,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7087,7 +7095,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7185,7 +7193,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7283,7 +7291,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7381,7 +7389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7479,7 +7487,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7577,7 +7585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7675,7 +7683,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7773,7 +7781,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7871,7 +7879,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7969,7 +7977,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8067,7 +8075,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8165,7 +8173,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8263,7 +8271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8361,7 +8369,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8459,7 +8467,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8557,7 +8565,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8655,7 +8663,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8753,7 +8761,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8851,7 +8859,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8949,7 +8957,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9047,7 +9055,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9145,7 +9153,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9243,7 +9251,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9341,7 +9349,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9439,7 +9447,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9537,7 +9545,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9635,7 +9643,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9733,7 +9741,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9831,7 +9839,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9929,7 +9937,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -10027,7 +10035,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -10125,7 +10133,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -10223,7 +10231,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10321,7 +10329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10419,7 +10427,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10517,7 +10525,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10615,7 +10623,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10713,7 +10721,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10811,7 +10819,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10909,7 +10917,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -11007,7 +11015,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -11105,7 +11113,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11203,7 +11211,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11301,7 +11309,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11399,7 +11407,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11497,7 +11505,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11595,7 +11603,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11693,7 +11701,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11791,7 +11799,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11889,7 +11897,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -11987,7 +11995,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12085,7 +12093,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12183,7 +12191,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12281,7 +12289,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12379,7 +12387,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12477,7 +12485,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12575,7 +12583,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12673,7 +12681,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12771,7 +12779,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -12869,7 +12877,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -12967,7 +12975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13065,7 +13073,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -13163,7 +13171,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -13261,7 +13269,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13359,7 +13367,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13457,7 +13465,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13555,7 +13563,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13653,7 +13661,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13751,7 +13759,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -13849,7 +13857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13947,7 +13955,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -14045,7 +14053,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -14143,7 +14151,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -14241,7 +14249,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -14339,7 +14347,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14437,7 +14445,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14535,7 +14543,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14633,7 +14641,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14731,7 +14739,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14829,7 +14837,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14927,7 +14935,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -15025,7 +15033,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -15123,7 +15131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -15221,7 +15229,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -15319,7 +15327,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -15417,7 +15425,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -15515,7 +15523,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -15613,7 +15621,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -15711,7 +15719,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -15809,7 +15817,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -15907,7 +15915,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -16005,7 +16013,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -16103,7 +16111,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -16201,7 +16209,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -16299,7 +16307,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -16397,7 +16405,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -16495,7 +16503,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -16593,7 +16601,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -16691,7 +16699,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -16789,7 +16797,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -16887,7 +16895,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -16985,7 +16993,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -17083,7 +17091,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -17181,7 +17189,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -17279,7 +17287,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -17377,7 +17385,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -17475,7 +17483,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -17573,7 +17581,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -17671,7 +17679,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -17769,7 +17777,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -17867,7 +17875,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -17965,7 +17973,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -18063,7 +18071,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -18161,7 +18169,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -18259,7 +18267,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -18357,1183 +18365,1183 @@
         <v>95</v>
       </c>
     </row>
-    <row r="157" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="4">
+    <row r="157" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
         <v>156</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C157" s="4" t="s">
+      <c r="C157" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D157" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E157" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F157" s="4">
+      <c r="D157" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F157" s="3">
         <v>2017</v>
       </c>
-      <c r="G157" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H157" s="4" t="s">
+      <c r="G157" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H157" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I157" s="4" t="s">
+      <c r="I157" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J157" s="4" t="s">
+      <c r="J157" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K157" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L157" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M157" s="5">
+      <c r="K157" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M157" s="4">
         <v>42854</v>
       </c>
-      <c r="N157" s="4">
+      <c r="N157" s="3">
         <v>47.222461000000003</v>
       </c>
-      <c r="O157" s="4">
+      <c r="O157" s="3">
         <v>-122.810239</v>
       </c>
-      <c r="P157" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q157" s="4" t="s">
+      <c r="P157" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q157" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R157" s="4">
+      <c r="R157" s="3">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="S157" s="4" t="s">
+      <c r="S157" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T157" s="4">
+      <c r="T157" s="3">
         <v>1</v>
       </c>
-      <c r="U157" s="4">
+      <c r="U157" s="3">
         <v>1</v>
       </c>
-      <c r="V157" s="4">
+      <c r="V157" s="3">
         <v>1</v>
       </c>
-      <c r="W157" s="4">
+      <c r="W157" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X157" s="4">
+      <c r="X157" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y157" s="4">
+      <c r="Y157" s="3">
         <v>3</v>
       </c>
-      <c r="Z157" s="4">
+      <c r="Z157" s="3">
         <v>12</v>
       </c>
-      <c r="AA157" s="4">
+      <c r="AA157" s="3">
         <v>12</v>
       </c>
-      <c r="AB157" s="4">
+      <c r="AB157" s="3">
         <v>1500</v>
       </c>
-      <c r="AC157" s="4" t="s">
+      <c r="AC157" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD157" s="4" t="s">
+      <c r="AD157" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE157" s="4" t="s">
+      <c r="AE157" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF157" s="4">
+      <c r="AF157" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="158" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="4">
+    <row r="158" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
         <v>157</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C158" s="4" t="s">
+      <c r="C158" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D158" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E158" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F158" s="4">
+      <c r="D158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F158" s="3">
         <v>2017</v>
       </c>
-      <c r="G158" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H158" s="4" t="s">
+      <c r="G158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H158" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I158" s="4" t="s">
+      <c r="I158" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J158" s="4" t="s">
+      <c r="J158" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K158" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L158" s="4" t="s">
+      <c r="K158" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L158" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M158" s="5">
+      <c r="M158" s="4">
         <v>42854</v>
       </c>
-      <c r="N158" s="4">
+      <c r="N158" s="3">
         <v>47.222489000000003</v>
       </c>
-      <c r="O158" s="4">
+      <c r="O158" s="3">
         <v>-122.81026199999999</v>
       </c>
-      <c r="P158" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q158" s="4" t="s">
+      <c r="P158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q158" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R158" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S158" s="4" t="s">
+      <c r="R158" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S158" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T158" s="4">
+      <c r="T158" s="3">
         <v>1</v>
       </c>
-      <c r="U158" s="4">
+      <c r="U158" s="3">
         <v>1</v>
       </c>
-      <c r="V158" s="4">
+      <c r="V158" s="3">
         <v>1</v>
       </c>
-      <c r="W158" s="4">
+      <c r="W158" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X158" s="4">
+      <c r="X158" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y158" s="4">
+      <c r="Y158" s="3">
         <v>3</v>
       </c>
-      <c r="Z158" s="4">
+      <c r="Z158" s="3">
         <v>12</v>
       </c>
-      <c r="AA158" s="4">
+      <c r="AA158" s="3">
         <v>12</v>
       </c>
-      <c r="AB158" s="4">
+      <c r="AB158" s="3">
         <v>1500</v>
       </c>
-      <c r="AC158" s="4" t="s">
+      <c r="AC158" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD158" s="4" t="s">
+      <c r="AD158" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE158" s="4" t="s">
+      <c r="AE158" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF158" s="4">
+      <c r="AF158" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="159" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="4">
+    <row r="159" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
         <v>158</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C159" s="4" t="s">
+      <c r="C159" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="D159" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E159" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F159" s="4">
+      <c r="D159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F159" s="3">
         <v>2017</v>
       </c>
-      <c r="G159" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H159" s="4" t="s">
+      <c r="G159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H159" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I159" s="4" t="s">
+      <c r="I159" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J159" s="4" t="s">
+      <c r="J159" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K159" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L159" s="4" t="s">
+      <c r="K159" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L159" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M159" s="5">
+      <c r="M159" s="4">
         <v>42854</v>
       </c>
-      <c r="N159" s="4">
+      <c r="N159" s="3">
         <v>47.222512000000002</v>
       </c>
-      <c r="O159" s="4">
+      <c r="O159" s="3">
         <v>-122.810267</v>
       </c>
-      <c r="P159" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q159" s="4" t="s">
+      <c r="P159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q159" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R159" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S159" s="4" t="s">
+      <c r="R159" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S159" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T159" s="4">
+      <c r="T159" s="3">
         <v>1</v>
       </c>
-      <c r="U159" s="4">
+      <c r="U159" s="3">
         <v>1</v>
       </c>
-      <c r="V159" s="4">
+      <c r="V159" s="3">
         <v>1</v>
       </c>
-      <c r="W159" s="4">
+      <c r="W159" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X159" s="4">
+      <c r="X159" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y159" s="4">
+      <c r="Y159" s="3">
         <v>3</v>
       </c>
-      <c r="Z159" s="4">
+      <c r="Z159" s="3">
         <v>12</v>
       </c>
-      <c r="AA159" s="4">
+      <c r="AA159" s="3">
         <v>12</v>
       </c>
-      <c r="AB159" s="4">
+      <c r="AB159" s="3">
         <v>1500</v>
       </c>
-      <c r="AC159" s="4" t="s">
+      <c r="AC159" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD159" s="4" t="s">
+      <c r="AD159" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE159" s="4" t="s">
+      <c r="AE159" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF159" s="4">
+      <c r="AF159" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="160" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="4">
+    <row r="160" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="3">
         <v>159</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C160" s="4" t="s">
+      <c r="C160" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D160" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E160" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F160" s="4">
+      <c r="D160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F160" s="3">
         <v>2017</v>
       </c>
-      <c r="G160" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H160" s="4" t="s">
+      <c r="G160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I160" s="4" t="s">
+      <c r="I160" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J160" s="4" t="s">
+      <c r="J160" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K160" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L160" s="4" t="s">
+      <c r="K160" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L160" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M160" s="5">
+      <c r="M160" s="4">
         <v>42854</v>
       </c>
-      <c r="N160" s="4">
+      <c r="N160" s="3">
         <v>47.222541999999997</v>
       </c>
-      <c r="O160" s="4">
+      <c r="O160" s="3">
         <v>-122.81027899999999</v>
       </c>
-      <c r="P160" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q160" s="4" t="s">
+      <c r="P160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q160" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R160" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S160" s="4" t="s">
+      <c r="R160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S160" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T160" s="4">
+      <c r="T160" s="3">
         <v>1</v>
       </c>
-      <c r="U160" s="4">
+      <c r="U160" s="3">
         <v>1</v>
       </c>
-      <c r="V160" s="4">
+      <c r="V160" s="3">
         <v>1</v>
       </c>
-      <c r="W160" s="4">
+      <c r="W160" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X160" s="4">
+      <c r="X160" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y160" s="4">
+      <c r="Y160" s="3">
         <v>3</v>
       </c>
-      <c r="Z160" s="4">
+      <c r="Z160" s="3">
         <v>12</v>
       </c>
-      <c r="AA160" s="4">
+      <c r="AA160" s="3">
         <v>12</v>
       </c>
-      <c r="AB160" s="4">
+      <c r="AB160" s="3">
         <v>1500</v>
       </c>
-      <c r="AC160" s="4" t="s">
+      <c r="AC160" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD160" s="4" t="s">
+      <c r="AD160" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE160" s="4" t="s">
+      <c r="AE160" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF160" s="4">
+      <c r="AF160" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="161" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="4">
+    <row r="161" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
         <v>160</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C161" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D161" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E161" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F161" s="4">
+      <c r="D161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F161" s="3">
         <v>2017</v>
       </c>
-      <c r="G161" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H161" s="4" t="s">
+      <c r="G161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H161" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I161" s="4" t="s">
+      <c r="I161" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J161" s="4" t="s">
+      <c r="J161" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K161" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L161" s="4" t="s">
+      <c r="K161" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L161" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M161" s="5">
+      <c r="M161" s="4">
         <v>42854</v>
       </c>
-      <c r="N161" s="4">
+      <c r="N161" s="3">
         <v>47.222552</v>
       </c>
-      <c r="O161" s="4">
+      <c r="O161" s="3">
         <v>-122.810293</v>
       </c>
-      <c r="P161" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q161" s="4" t="s">
+      <c r="P161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q161" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R161" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S161" s="4" t="s">
+      <c r="R161" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S161" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T161" s="4">
+      <c r="T161" s="3">
         <v>1</v>
       </c>
-      <c r="U161" s="4">
+      <c r="U161" s="3">
         <v>1</v>
       </c>
-      <c r="V161" s="4">
+      <c r="V161" s="3">
         <v>1</v>
       </c>
-      <c r="W161" s="4">
+      <c r="W161" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X161" s="4">
+      <c r="X161" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y161" s="4">
+      <c r="Y161" s="3">
         <v>3</v>
       </c>
-      <c r="Z161" s="4">
+      <c r="Z161" s="3">
         <v>12</v>
       </c>
-      <c r="AA161" s="4">
+      <c r="AA161" s="3">
         <v>12</v>
       </c>
-      <c r="AB161" s="4">
+      <c r="AB161" s="3">
         <v>1500</v>
       </c>
-      <c r="AC161" s="4" t="s">
+      <c r="AC161" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD161" s="4" t="s">
+      <c r="AD161" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE161" s="4" t="s">
+      <c r="AE161" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF161" s="4">
+      <c r="AF161" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="162" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="4">
+    <row r="162" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3">
         <v>161</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C162" s="4" t="s">
+      <c r="C162" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D162" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E162" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F162" s="4">
+      <c r="D162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F162" s="3">
         <v>2017</v>
       </c>
-      <c r="G162" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H162" s="4" t="s">
+      <c r="G162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H162" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I162" s="4" t="s">
+      <c r="I162" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J162" s="4" t="s">
+      <c r="J162" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K162" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L162" s="4" t="s">
+      <c r="K162" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L162" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M162" s="5">
+      <c r="M162" s="4">
         <v>42854</v>
       </c>
-      <c r="N162" s="4">
+      <c r="N162" s="3">
         <v>47.222596000000003</v>
       </c>
-      <c r="O162" s="4">
+      <c r="O162" s="3">
         <v>-122.810309</v>
       </c>
-      <c r="P162" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q162" s="4" t="s">
+      <c r="P162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q162" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R162" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S162" s="4" t="s">
+      <c r="R162" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S162" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T162" s="4">
+      <c r="T162" s="3">
         <v>1</v>
       </c>
-      <c r="U162" s="4">
+      <c r="U162" s="3">
         <v>1</v>
       </c>
-      <c r="V162" s="4">
+      <c r="V162" s="3">
         <v>1</v>
       </c>
-      <c r="W162" s="4">
+      <c r="W162" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X162" s="4">
+      <c r="X162" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y162" s="4">
+      <c r="Y162" s="3">
         <v>3</v>
       </c>
-      <c r="Z162" s="4">
+      <c r="Z162" s="3">
         <v>12</v>
       </c>
-      <c r="AA162" s="4">
+      <c r="AA162" s="3">
         <v>12</v>
       </c>
-      <c r="AB162" s="4">
+      <c r="AB162" s="3">
         <v>1500</v>
       </c>
-      <c r="AC162" s="4" t="s">
+      <c r="AC162" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD162" s="4" t="s">
+      <c r="AD162" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE162" s="4" t="s">
+      <c r="AE162" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF162" s="4">
+      <c r="AF162" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="163" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="4">
+    <row r="163" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="3">
         <v>162</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C163" s="4" t="s">
+      <c r="C163" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D163" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E163" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F163" s="4">
+      <c r="D163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F163" s="3">
         <v>2017</v>
       </c>
-      <c r="G163" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H163" s="4" t="s">
+      <c r="G163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H163" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I163" s="4" t="s">
+      <c r="I163" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J163" s="4" t="s">
+      <c r="J163" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K163" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L163" s="4" t="s">
+      <c r="K163" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L163" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M163" s="5">
+      <c r="M163" s="4">
         <v>42854</v>
       </c>
-      <c r="N163" s="4">
+      <c r="N163" s="3">
         <v>47.222611999999998</v>
       </c>
-      <c r="O163" s="4">
+      <c r="O163" s="3">
         <v>-122.810312</v>
       </c>
-      <c r="P163" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q163" s="4" t="s">
+      <c r="P163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q163" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R163" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S163" s="4" t="s">
+      <c r="R163" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S163" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T163" s="4">
+      <c r="T163" s="3">
         <v>1</v>
       </c>
-      <c r="U163" s="4">
+      <c r="U163" s="3">
         <v>1</v>
       </c>
-      <c r="V163" s="4">
+      <c r="V163" s="3">
         <v>1</v>
       </c>
-      <c r="W163" s="4">
+      <c r="W163" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X163" s="4">
+      <c r="X163" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y163" s="4">
+      <c r="Y163" s="3">
         <v>3</v>
       </c>
-      <c r="Z163" s="4">
+      <c r="Z163" s="3">
         <v>12</v>
       </c>
-      <c r="AA163" s="4">
+      <c r="AA163" s="3">
         <v>12</v>
       </c>
-      <c r="AB163" s="4">
+      <c r="AB163" s="3">
         <v>1500</v>
       </c>
-      <c r="AC163" s="4" t="s">
+      <c r="AC163" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD163" s="4" t="s">
+      <c r="AD163" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE163" s="4" t="s">
+      <c r="AE163" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF163" s="4">
+      <c r="AF163" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="164" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="4">
+    <row r="164" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="3">
         <v>163</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C164" s="4" t="s">
+      <c r="C164" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D164" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E164" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F164" s="4">
+      <c r="D164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F164" s="3">
         <v>2017</v>
       </c>
-      <c r="G164" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H164" s="4" t="s">
+      <c r="G164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H164" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I164" s="4" t="s">
+      <c r="I164" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J164" s="4" t="s">
+      <c r="J164" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K164" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L164" s="4" t="s">
+      <c r="K164" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L164" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M164" s="5">
+      <c r="M164" s="4">
         <v>42854</v>
       </c>
-      <c r="N164" s="4">
+      <c r="N164" s="3">
         <v>47.222638000000003</v>
       </c>
-      <c r="O164" s="4">
+      <c r="O164" s="3">
         <v>-122.810339</v>
       </c>
-      <c r="P164" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q164" s="4" t="s">
+      <c r="P164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q164" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R164" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S164" s="4" t="s">
+      <c r="R164" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S164" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T164" s="4">
+      <c r="T164" s="3">
         <v>1</v>
       </c>
-      <c r="U164" s="4">
+      <c r="U164" s="3">
         <v>1</v>
       </c>
-      <c r="V164" s="4">
+      <c r="V164" s="3">
         <v>1</v>
       </c>
-      <c r="W164" s="4">
+      <c r="W164" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X164" s="4">
+      <c r="X164" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y164" s="4">
+      <c r="Y164" s="3">
         <v>3</v>
       </c>
-      <c r="Z164" s="4">
+      <c r="Z164" s="3">
         <v>12</v>
       </c>
-      <c r="AA164" s="4">
+      <c r="AA164" s="3">
         <v>12</v>
       </c>
-      <c r="AB164" s="4">
+      <c r="AB164" s="3">
         <v>1500</v>
       </c>
-      <c r="AC164" s="4" t="s">
+      <c r="AC164" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD164" s="4" t="s">
+      <c r="AD164" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE164" s="4" t="s">
+      <c r="AE164" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF164" s="4">
+      <c r="AF164" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="165" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="4">
+    <row r="165" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3">
         <v>164</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C165" s="4" t="s">
+      <c r="C165" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="D165" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E165" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F165" s="4">
+      <c r="D165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F165" s="3">
         <v>2017</v>
       </c>
-      <c r="G165" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H165" s="4" t="s">
+      <c r="G165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I165" s="4" t="s">
+      <c r="I165" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J165" s="4" t="s">
+      <c r="J165" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K165" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L165" s="4" t="s">
+      <c r="K165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L165" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M165" s="5">
+      <c r="M165" s="4">
         <v>42854</v>
       </c>
-      <c r="N165" s="4">
+      <c r="N165" s="3">
         <v>47.222659</v>
       </c>
-      <c r="O165" s="4">
+      <c r="O165" s="3">
         <v>-122.810361</v>
       </c>
-      <c r="P165" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q165" s="4" t="s">
+      <c r="P165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q165" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R165" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S165" s="4" t="s">
+      <c r="R165" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S165" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T165" s="4">
+      <c r="T165" s="3">
         <v>1</v>
       </c>
-      <c r="U165" s="4">
+      <c r="U165" s="3">
         <v>1</v>
       </c>
-      <c r="V165" s="4">
+      <c r="V165" s="3">
         <v>1</v>
       </c>
-      <c r="W165" s="4">
+      <c r="W165" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X165" s="4">
+      <c r="X165" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y165" s="4">
+      <c r="Y165" s="3">
         <v>3</v>
       </c>
-      <c r="Z165" s="4">
+      <c r="Z165" s="3">
         <v>12</v>
       </c>
-      <c r="AA165" s="4">
+      <c r="AA165" s="3">
         <v>12</v>
       </c>
-      <c r="AB165" s="4">
+      <c r="AB165" s="3">
         <v>1500</v>
       </c>
-      <c r="AC165" s="4" t="s">
+      <c r="AC165" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD165" s="4" t="s">
+      <c r="AD165" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE165" s="4" t="s">
+      <c r="AE165" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF165" s="4">
+      <c r="AF165" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="166" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="4">
+    <row r="166" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="3">
         <v>165</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C166" s="4" t="s">
+      <c r="C166" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D166" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E166" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F166" s="4">
+      <c r="D166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F166" s="3">
         <v>2017</v>
       </c>
-      <c r="G166" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H166" s="4" t="s">
+      <c r="G166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H166" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I166" s="4" t="s">
+      <c r="I166" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J166" s="4" t="s">
+      <c r="J166" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K166" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L166" s="4" t="s">
+      <c r="K166" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L166" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M166" s="5">
+      <c r="M166" s="4">
         <v>42854</v>
       </c>
-      <c r="N166" s="4">
+      <c r="N166" s="3">
         <v>47.222687999999998</v>
       </c>
-      <c r="O166" s="4">
+      <c r="O166" s="3">
         <v>-122.810372</v>
       </c>
-      <c r="P166" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q166" s="4" t="s">
+      <c r="P166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q166" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R166" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S166" s="4" t="s">
+      <c r="R166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S166" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T166" s="4">
+      <c r="T166" s="3">
         <v>1</v>
       </c>
-      <c r="U166" s="4">
+      <c r="U166" s="3">
         <v>1</v>
       </c>
-      <c r="V166" s="4">
+      <c r="V166" s="3">
         <v>1</v>
       </c>
-      <c r="W166" s="4">
+      <c r="W166" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X166" s="4">
+      <c r="X166" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y166" s="4">
+      <c r="Y166" s="3">
         <v>3</v>
       </c>
-      <c r="Z166" s="4">
+      <c r="Z166" s="3">
         <v>12</v>
       </c>
-      <c r="AA166" s="4">
+      <c r="AA166" s="3">
         <v>12</v>
       </c>
-      <c r="AB166" s="4">
+      <c r="AB166" s="3">
         <v>1500</v>
       </c>
-      <c r="AC166" s="4" t="s">
+      <c r="AC166" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD166" s="4" t="s">
+      <c r="AD166" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE166" s="4" t="s">
+      <c r="AE166" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF166" s="4">
+      <c r="AF166" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="167" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="4">
+    <row r="167" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="3">
         <v>166</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C167" s="4" t="s">
+      <c r="C167" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D167" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F167" s="4">
+      <c r="D167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F167" s="3">
         <v>2017</v>
       </c>
-      <c r="G167" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H167" s="4" t="s">
+      <c r="G167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H167" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I167" s="4" t="s">
+      <c r="I167" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J167" s="4" t="s">
+      <c r="J167" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K167" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L167" s="4" t="s">
+      <c r="K167" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L167" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M167" s="5">
+      <c r="M167" s="4">
         <v>42854</v>
       </c>
-      <c r="N167" s="4">
+      <c r="N167" s="3">
         <v>47.222720000000002</v>
       </c>
-      <c r="O167" s="4">
+      <c r="O167" s="3">
         <v>-122.81038599999999</v>
       </c>
-      <c r="P167" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q167" s="4" t="s">
+      <c r="P167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q167" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R167" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S167" s="4" t="s">
+      <c r="R167" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S167" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T167" s="4">
+      <c r="T167" s="3">
         <v>1</v>
       </c>
-      <c r="U167" s="4">
+      <c r="U167" s="3">
         <v>1</v>
       </c>
-      <c r="V167" s="4">
+      <c r="V167" s="3">
         <v>1</v>
       </c>
-      <c r="W167" s="4">
+      <c r="W167" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X167" s="4">
+      <c r="X167" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y167" s="4">
+      <c r="Y167" s="3">
         <v>3</v>
       </c>
-      <c r="Z167" s="4">
+      <c r="Z167" s="3">
         <v>12</v>
       </c>
-      <c r="AA167" s="4">
+      <c r="AA167" s="3">
         <v>12</v>
       </c>
-      <c r="AB167" s="4">
+      <c r="AB167" s="3">
         <v>1500</v>
       </c>
-      <c r="AC167" s="4" t="s">
+      <c r="AC167" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD167" s="4" t="s">
+      <c r="AD167" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE167" s="4" t="s">
+      <c r="AE167" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF167" s="4">
+      <c r="AF167" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="168" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="4">
+    <row r="168" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3">
         <v>167</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C168" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D168" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F168" s="4">
+      <c r="D168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F168" s="3">
         <v>2017</v>
       </c>
-      <c r="G168" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H168" s="4" t="s">
+      <c r="G168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H168" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I168" s="4" t="s">
+      <c r="I168" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J168" s="4" t="s">
+      <c r="J168" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K168" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L168" s="4" t="s">
+      <c r="K168" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L168" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M168" s="5">
+      <c r="M168" s="4">
         <v>42854</v>
       </c>
-      <c r="N168" s="4">
+      <c r="N168" s="3">
         <v>47.222732999999998</v>
       </c>
-      <c r="O168" s="4">
+      <c r="O168" s="3">
         <v>-122.8104</v>
       </c>
-      <c r="P168" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q168" s="4" t="s">
+      <c r="P168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q168" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R168" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S168" s="4" t="s">
+      <c r="R168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S168" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T168" s="4">
+      <c r="T168" s="3">
         <v>1</v>
       </c>
-      <c r="U168" s="4">
+      <c r="U168" s="3">
         <v>1</v>
       </c>
-      <c r="V168" s="4">
+      <c r="V168" s="3">
         <v>1</v>
       </c>
-      <c r="W168" s="4">
+      <c r="W168" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="X168" s="4">
+      <c r="X168" s="3">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Y168" s="4">
+      <c r="Y168" s="3">
         <v>3</v>
       </c>
-      <c r="Z168" s="4">
+      <c r="Z168" s="3">
         <v>12</v>
       </c>
-      <c r="AA168" s="4">
+      <c r="AA168" s="3">
         <v>12</v>
       </c>
-      <c r="AB168" s="4">
+      <c r="AB168" s="3">
         <v>1500</v>
       </c>
-      <c r="AC168" s="4" t="s">
+      <c r="AC168" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD168" s="4" t="s">
+      <c r="AD168" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AE168" s="4" t="s">
+      <c r="AE168" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AF168" s="4">
+      <c r="AF168" s="3">
         <v>96</v>
       </c>
     </row>
-    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -19631,7 +19639,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -19729,7 +19737,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -19827,7 +19835,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -19925,7 +19933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -20023,7 +20031,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -20121,7 +20129,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -20219,7 +20227,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -20317,7 +20325,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -20415,7 +20423,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -20513,7 +20521,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -20611,7 +20619,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -20709,7 +20717,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -20807,7 +20815,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -20905,7 +20913,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -21003,7 +21011,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -21101,7 +21109,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -21199,7 +21207,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -21297,7 +21305,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -21395,7 +21403,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -21493,7 +21501,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -21591,7 +21599,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -21689,7 +21697,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -21787,7 +21795,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -21885,7 +21893,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -21983,7 +21991,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -22081,7 +22089,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -22179,7 +22187,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -22277,7 +22285,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -22375,7 +22383,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -22473,7 +22481,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -22571,7 +22579,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -22669,7 +22677,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -22767,7 +22775,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -22865,7 +22873,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -22963,7 +22971,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -23061,7 +23069,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -23159,7 +23167,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -23257,7 +23265,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -23355,7 +23363,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -23453,7 +23461,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -23551,7 +23559,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -23649,7 +23657,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -23747,7 +23755,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -23845,7 +23853,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -23943,7 +23951,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -24041,7 +24049,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -24139,7 +24147,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="216" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -24237,7 +24245,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="217" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -24335,7 +24343,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -24433,7 +24441,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -24531,7 +24539,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -24629,7 +24637,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="221" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -24727,7 +24735,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -24825,7 +24833,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="223" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -24923,7 +24931,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="224" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -25021,7 +25029,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="225" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -25119,7 +25127,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="226" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -25217,7 +25225,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="227" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -25315,7 +25323,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="228" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -25413,7 +25421,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="229" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -25511,7 +25519,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="230" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -25609,7 +25617,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="231" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -25707,7 +25715,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="232" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -25805,7 +25813,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="233" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -25903,7 +25911,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="234" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -26001,7 +26009,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="235" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -26099,7 +26107,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="236" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -26197,7 +26205,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="237" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -26295,7 +26303,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="238" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -26393,7 +26401,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="239" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -26491,7 +26499,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="240" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -26589,7 +26597,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="241" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -26687,7 +26695,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="242" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -26785,7 +26793,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="243" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -26883,7 +26891,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="244" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -26981,7 +26989,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="245" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -27079,693 +27087,693 @@
         <v>156</v>
       </c>
     </row>
-    <row r="246" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="4">
+    <row r="246" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="3">
         <v>245</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C246" s="4" t="s">
+      <c r="C246" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D246" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E246" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F246" s="4">
+      <c r="D246" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F246" s="3">
         <v>2021</v>
       </c>
-      <c r="G246" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H246" s="4" t="s">
+      <c r="G246" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H246" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I246" s="4" t="s">
+      <c r="I246" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J246" s="4" t="s">
+      <c r="J246" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K246" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L246" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M246" s="5">
+      <c r="K246" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L246" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M246" s="4">
         <v>44329</v>
       </c>
-      <c r="N246" s="4">
+      <c r="N246" s="3">
         <v>47.390659999999997</v>
       </c>
-      <c r="O246" s="4">
+      <c r="O246" s="3">
         <v>-122.43606</v>
       </c>
-      <c r="P246" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q246" s="4" t="s">
+      <c r="P246" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q246" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R246" s="4">
+      <c r="R246" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S246" s="4" t="s">
+      <c r="S246" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T246" s="4">
+      <c r="T246" s="3">
         <v>3.5</v>
       </c>
-      <c r="U246" s="4">
+      <c r="U246" s="3">
         <v>0.5</v>
       </c>
-      <c r="V246" s="4">
+      <c r="V246" s="3">
         <v>1.75</v>
       </c>
-      <c r="W246" s="4">
+      <c r="W246" s="3">
         <v>1</v>
       </c>
-      <c r="X246" s="4">
+      <c r="X246" s="3">
         <v>0.3</v>
       </c>
-      <c r="Y246" s="4">
+      <c r="Y246" s="3">
         <v>12</v>
       </c>
-      <c r="Z246" s="4">
+      <c r="Z246" s="3">
         <v>240</v>
       </c>
-      <c r="AA246" s="4">
+      <c r="AA246" s="3">
         <v>137.142857142857</v>
       </c>
-      <c r="AB246" s="4">
+      <c r="AB246" s="3">
         <v>240</v>
       </c>
-      <c r="AC246" s="4" t="s">
+      <c r="AC246" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AD246" s="4" t="s">
+      <c r="AD246" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="AE246" s="4" t="s">
+      <c r="AE246" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF246" s="4">
+      <c r="AF246" s="3">
         <v>157</v>
       </c>
     </row>
-    <row r="247" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="4">
+    <row r="247" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="3">
         <v>246</v>
       </c>
-      <c r="B247" s="4" t="s">
+      <c r="B247" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C247" s="4" t="s">
+      <c r="C247" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D247" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E247" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F247" s="4">
+      <c r="D247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F247" s="3">
         <v>2021</v>
       </c>
-      <c r="G247" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H247" s="4" t="s">
+      <c r="G247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H247" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I247" s="4" t="s">
+      <c r="I247" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J247" s="4" t="s">
+      <c r="J247" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K247" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L247" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M247" s="5">
+      <c r="K247" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L247" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M247" s="4">
         <v>44330</v>
       </c>
-      <c r="N247" s="4">
+      <c r="N247" s="3">
         <v>47.390659999999997</v>
       </c>
-      <c r="O247" s="4">
+      <c r="O247" s="3">
         <v>-122.43606</v>
       </c>
-      <c r="P247" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q247" s="4" t="s">
+      <c r="P247" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q247" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R247" s="4">
+      <c r="R247" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S247" s="4" t="s">
+      <c r="S247" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T247" s="4">
+      <c r="T247" s="3">
         <v>4.5</v>
       </c>
-      <c r="U247" s="4">
+      <c r="U247" s="3">
         <v>0.5</v>
       </c>
-      <c r="V247" s="4">
+      <c r="V247" s="3">
         <v>2.25</v>
       </c>
-      <c r="W247" s="4">
+      <c r="W247" s="3">
         <v>1.25</v>
       </c>
-      <c r="X247" s="4">
+      <c r="X247" s="3">
         <v>0.375</v>
       </c>
-      <c r="Y247" s="4">
+      <c r="Y247" s="3">
         <v>15</v>
       </c>
-      <c r="Z247" s="4">
+      <c r="Z247" s="3">
         <v>375</v>
       </c>
-      <c r="AA247" s="4">
+      <c r="AA247" s="3">
         <v>166.666666666667</v>
       </c>
-      <c r="AB247" s="4">
+      <c r="AB247" s="3">
         <v>300</v>
       </c>
-      <c r="AC247" s="4" t="s">
+      <c r="AC247" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD247" s="4" t="s">
+      <c r="AD247" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="AE247" s="4" t="s">
+      <c r="AE247" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF247" s="4">
+      <c r="AF247" s="3">
         <v>158</v>
       </c>
     </row>
-    <row r="248" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="4">
+    <row r="248" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="3">
         <v>247</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C248" s="4" t="s">
+      <c r="C248" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D248" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E248" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F248" s="4">
+      <c r="D248" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F248" s="3">
         <v>2021</v>
       </c>
-      <c r="G248" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H248" s="4" t="s">
+      <c r="G248" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H248" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I248" s="4" t="s">
+      <c r="I248" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J248" s="4" t="s">
+      <c r="J248" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K248" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L248" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M248" s="5">
+      <c r="K248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M248" s="4">
         <v>44342</v>
       </c>
-      <c r="N248" s="4">
+      <c r="N248" s="3">
         <v>47.390659999999997</v>
       </c>
-      <c r="O248" s="4">
+      <c r="O248" s="3">
         <v>-122.43606</v>
       </c>
-      <c r="P248" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q248" s="4" t="s">
+      <c r="P248" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q248" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R248" s="4">
+      <c r="R248" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S248" s="4" t="s">
+      <c r="S248" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T248" s="4">
+      <c r="T248" s="3">
         <v>2.5</v>
       </c>
-      <c r="U248" s="4">
+      <c r="U248" s="3">
         <v>1</v>
       </c>
-      <c r="V248" s="4">
+      <c r="V248" s="3">
         <v>2.5</v>
       </c>
-      <c r="W248" s="4">
+      <c r="W248" s="3">
         <v>1.5</v>
       </c>
-      <c r="X248" s="4">
+      <c r="X248" s="3">
         <v>0.45</v>
       </c>
-      <c r="Y248" s="4">
+      <c r="Y248" s="3">
         <v>18</v>
       </c>
-      <c r="Z248" s="4">
+      <c r="Z248" s="3">
         <v>270</v>
       </c>
-      <c r="AA248" s="4">
+      <c r="AA248" s="3">
         <v>108</v>
       </c>
-      <c r="AB248" s="4">
+      <c r="AB248" s="3">
         <v>180</v>
       </c>
-      <c r="AC248" s="4" t="s">
+      <c r="AC248" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AD248" s="4" t="s">
+      <c r="AD248" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="AE248" s="4" t="s">
+      <c r="AE248" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF248" s="4">
+      <c r="AF248" s="3">
         <v>159</v>
       </c>
     </row>
-    <row r="249" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="4">
+    <row r="249" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="3">
         <v>248</v>
       </c>
-      <c r="B249" s="4" t="s">
+      <c r="B249" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C249" s="4" t="s">
+      <c r="C249" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="D249" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E249" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F249" s="4">
+      <c r="D249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F249" s="3">
         <v>2021</v>
       </c>
-      <c r="G249" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H249" s="4" t="s">
+      <c r="G249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H249" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I249" s="4" t="s">
+      <c r="I249" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J249" s="4" t="s">
+      <c r="J249" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K249" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L249" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M249" s="5">
+      <c r="K249" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L249" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M249" s="4">
         <v>44329</v>
       </c>
-      <c r="N249" s="4">
+      <c r="N249" s="3">
         <v>47.385899999999999</v>
       </c>
-      <c r="O249" s="4">
+      <c r="O249" s="3">
         <v>-122.4379</v>
       </c>
-      <c r="P249" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q249" s="4" t="s">
+      <c r="P249" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q249" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R249" s="4">
+      <c r="R249" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S249" s="4" t="s">
+      <c r="S249" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T249" s="4">
+      <c r="T249" s="3">
         <v>2.5</v>
       </c>
-      <c r="U249" s="4">
+      <c r="U249" s="3">
         <v>0.5</v>
       </c>
-      <c r="V249" s="4">
+      <c r="V249" s="3">
         <v>1.25</v>
       </c>
-      <c r="W249" s="4">
+      <c r="W249" s="3">
         <v>0.75</v>
       </c>
-      <c r="X249" s="4">
+      <c r="X249" s="3">
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y249" s="4">
+      <c r="Y249" s="3">
         <v>9</v>
       </c>
-      <c r="Z249" s="4">
+      <c r="Z249" s="3">
         <v>180</v>
       </c>
-      <c r="AA249" s="4">
+      <c r="AA249" s="3">
         <v>144</v>
       </c>
-      <c r="AB249" s="4">
+      <c r="AB249" s="3">
         <v>240</v>
       </c>
-      <c r="AC249" s="4" t="s">
+      <c r="AC249" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AD249" s="4" t="s">
+      <c r="AD249" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="AE249" s="4" t="s">
+      <c r="AE249" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF249" s="4">
+      <c r="AF249" s="3">
         <v>160</v>
       </c>
     </row>
-    <row r="250" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="4">
+    <row r="250" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A250" s="3">
         <v>249</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C250" s="4" t="s">
+      <c r="C250" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="D250" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E250" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F250" s="4">
+      <c r="D250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F250" s="3">
         <v>2021</v>
       </c>
-      <c r="G250" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H250" s="4" t="s">
+      <c r="G250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H250" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I250" s="4" t="s">
+      <c r="I250" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J250" s="4" t="s">
+      <c r="J250" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K250" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L250" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M250" s="5">
+      <c r="K250" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L250" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M250" s="4">
         <v>44330</v>
       </c>
-      <c r="N250" s="4">
+      <c r="N250" s="3">
         <v>47.385899999999999</v>
       </c>
-      <c r="O250" s="4">
+      <c r="O250" s="3">
         <v>-122.4379</v>
       </c>
-      <c r="P250" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q250" s="4" t="s">
+      <c r="P250" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q250" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R250" s="4">
+      <c r="R250" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S250" s="4" t="s">
+      <c r="S250" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T250" s="4">
+      <c r="T250" s="3">
         <v>2.5</v>
       </c>
-      <c r="U250" s="4">
+      <c r="U250" s="3">
         <v>0.5</v>
       </c>
-      <c r="V250" s="4">
+      <c r="V250" s="3">
         <v>1.25</v>
       </c>
-      <c r="W250" s="4">
+      <c r="W250" s="3">
         <v>0.75</v>
       </c>
-      <c r="X250" s="4">
+      <c r="X250" s="3">
         <v>0.22500000000000001</v>
       </c>
-      <c r="Y250" s="4">
+      <c r="Y250" s="3">
         <v>9</v>
       </c>
-      <c r="Z250" s="4">
+      <c r="Z250" s="3">
         <v>180</v>
       </c>
-      <c r="AA250" s="4">
+      <c r="AA250" s="3">
         <v>144</v>
       </c>
-      <c r="AB250" s="4">
+      <c r="AB250" s="3">
         <v>240</v>
       </c>
-      <c r="AC250" s="4" t="s">
+      <c r="AC250" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="AD250" s="4" t="s">
+      <c r="AD250" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="AE250" s="4" t="s">
+      <c r="AE250" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF250" s="4">
+      <c r="AF250" s="3">
         <v>161</v>
       </c>
     </row>
-    <row r="251" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="4">
+    <row r="251" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="3">
         <v>250</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C251" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D251" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E251" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F251" s="4">
+      <c r="D251" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F251" s="3">
         <v>2021</v>
       </c>
-      <c r="G251" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H251" s="4" t="s">
+      <c r="G251" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H251" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I251" s="4" t="s">
+      <c r="I251" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J251" s="4" t="s">
+      <c r="J251" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K251" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L251" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M251" s="5">
+      <c r="K251" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L251" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M251" s="4">
         <v>44342</v>
       </c>
-      <c r="N251" s="4">
+      <c r="N251" s="3">
         <v>47.390659999999997</v>
       </c>
-      <c r="O251" s="4">
+      <c r="O251" s="3">
         <v>-122.43606</v>
       </c>
-      <c r="P251" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q251" s="4" t="s">
+      <c r="P251" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q251" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R251" s="4">
+      <c r="R251" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S251" s="4" t="s">
+      <c r="S251" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="T251" s="4">
+      <c r="T251" s="3">
         <v>2.5</v>
       </c>
-      <c r="U251" s="4">
+      <c r="U251" s="3">
         <v>1</v>
       </c>
-      <c r="V251" s="4">
+      <c r="V251" s="3">
         <v>2.5</v>
       </c>
-      <c r="W251" s="4">
+      <c r="W251" s="3">
         <v>4.5</v>
       </c>
-      <c r="X251" s="4">
+      <c r="X251" s="3">
         <v>0.45</v>
       </c>
-      <c r="Y251" s="4">
+      <c r="Y251" s="3">
         <v>18</v>
       </c>
-      <c r="Z251" s="4">
+      <c r="Z251" s="3">
         <v>360</v>
       </c>
-      <c r="AA251" s="4">
+      <c r="AA251" s="3">
         <v>144</v>
       </c>
-      <c r="AB251" s="4">
+      <c r="AB251" s="3">
         <v>80</v>
       </c>
-      <c r="AC251" s="4" t="s">
+      <c r="AC251" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AD251" s="4" t="s">
+      <c r="AD251" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="AE251" s="4" t="s">
+      <c r="AE251" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF251" s="4">
+      <c r="AF251" s="3">
         <v>162</v>
       </c>
     </row>
-    <row r="252" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="4">
+    <row r="252" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="3">
         <v>251</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C252" s="4" t="s">
+      <c r="C252" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="D252" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E252" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F252" s="4">
+      <c r="D252" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F252" s="3">
         <v>2022</v>
       </c>
-      <c r="G252" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H252" s="4" t="s">
+      <c r="G252" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H252" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I252" s="4" t="s">
+      <c r="I252" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J252" s="4" t="s">
+      <c r="J252" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K252" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L252" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M252" s="5">
+      <c r="K252" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L252" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M252" s="4">
         <v>44700</v>
       </c>
-      <c r="N252" s="4">
+      <c r="N252" s="3">
         <v>47.390659999999997</v>
       </c>
-      <c r="O252" s="4">
+      <c r="O252" s="3">
         <v>-122.43606</v>
       </c>
-      <c r="P252" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q252" s="4" t="s">
+      <c r="P252" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q252" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="R252" s="4">
+      <c r="R252" s="3">
         <v>-1.5</v>
       </c>
-      <c r="S252" s="4" t="s">
+      <c r="S252" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="T252" s="4">
+      <c r="T252" s="3">
         <v>1.5</v>
       </c>
-      <c r="U252" s="4">
+      <c r="U252" s="3">
         <v>0.5</v>
       </c>
-      <c r="V252" s="4">
+      <c r="V252" s="3">
         <v>0.75</v>
       </c>
-      <c r="W252" s="4">
+      <c r="W252" s="3">
         <v>0.75</v>
       </c>
-      <c r="X252" s="4">
+      <c r="X252" s="3">
         <v>0.75</v>
       </c>
-      <c r="Y252" s="4">
+      <c r="Y252" s="3">
         <v>3</v>
       </c>
-      <c r="Z252" s="4">
+      <c r="Z252" s="3">
         <v>75</v>
       </c>
-      <c r="AA252" s="4">
+      <c r="AA252" s="3">
         <v>100</v>
       </c>
-      <c r="AB252" s="4">
+      <c r="AB252" s="3">
         <v>100</v>
       </c>
-      <c r="AC252" s="4" t="s">
+      <c r="AC252" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AD252" s="4" t="s">
+      <c r="AD252" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="AE252" s="4" t="s">
+      <c r="AE252" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="AF252" s="4">
+      <c r="AF252" s="3">
         <v>163</v>
       </c>
     </row>
-    <row r="253" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -27863,7 +27871,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="254" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -27961,7 +27969,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="255" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -28059,7 +28067,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="256" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -28157,7 +28165,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="257" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -28255,7 +28263,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="258" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -28353,7 +28361,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="259" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -28451,7 +28459,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="260" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -28549,7 +28557,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="261" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -28647,7 +28655,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="262" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -28745,7 +28753,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="263" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -28843,7 +28851,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="264" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -28941,7 +28949,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="265" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -29039,7 +29047,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="266" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -29137,7 +29145,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="267" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -29235,7 +29243,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="268" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -29333,7 +29341,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="269" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -29431,7 +29439,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="270" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -29529,7 +29537,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="271" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -29627,7 +29635,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="272" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -29725,7 +29733,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="273" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -29823,7 +29831,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="274" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -29921,7 +29929,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="275" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -30019,7 +30027,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="276" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -30117,7 +30125,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="277" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -30215,7 +30223,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="278" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -30313,7 +30321,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="279" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -30411,7 +30419,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="280" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -30509,7 +30517,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="281" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -30607,7 +30615,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="282" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -30705,7 +30713,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="283" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -30803,7 +30811,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="284" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -30901,7 +30909,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="285" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -30999,7 +31007,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="286" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -31097,7 +31105,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="287" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -31195,7 +31203,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="288" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -31293,7 +31301,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="289" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>

--- a/p_gps_pts1_groupno.xlsx
+++ b/p_gps_pts1_groupno.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/91aba14b6835b0ae/Work-current/Restoration_Storymap/2026_02_update/home_mbp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{E27E93FE-057A-433C-80E8-4BF8A3DA57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F935D0A7-7E34-4E18-A911-5DCEEEBA1BB3}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{E27E93FE-057A-433C-80E8-4BF8A3DA57B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CA58D72-F677-1C43-8559-E8A4167EBBC2}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="45" windowWidth="28320" windowHeight="15315" xr2:uid="{05EB62A8-AD25-4BA7-B277-61FA4B199BDB}"/>
+    <workbookView xWindow="480" yWindow="600" windowWidth="35000" windowHeight="21360" xr2:uid="{05EB62A8-AD25-4BA7-B277-61FA4B199BDB}"/>
   </bookViews>
   <sheets>
     <sheet name="p_gps_pts1_groupno" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5404" uniqueCount="711">
   <si>
     <t>site_location</t>
   </si>
@@ -2141,13 +2154,28 @@
   </si>
   <si>
     <t>4, 0.0625 m2 rebar quads planted (chia pets)</t>
+  </si>
+  <si>
+    <t>group count</t>
+  </si>
+  <si>
+    <t>multi cases</t>
+  </si>
+  <si>
+    <t>geom</t>
+  </si>
+  <si>
+    <t>bese reps</t>
+  </si>
+  <si>
+    <t>QMH reps</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2286,6 +2314,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2659,7 +2694,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2668,6 +2703,7 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3043,44 +3079,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5B52F13-8966-47C6-8960-2C41BC3E18EA}">
-  <dimension ref="A1:AF289"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI289"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.5703125" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.5" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="5" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.5703125" customWidth="1"/>
-    <col min="21" max="21" width="23.5703125" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" customWidth="1"/>
-    <col min="23" max="23" width="17" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" customWidth="1"/>
-    <col min="25" max="25" width="22.28515625" customWidth="1"/>
-    <col min="26" max="26" width="15.28515625" customWidth="1"/>
-    <col min="27" max="27" width="22.42578125" customWidth="1"/>
-    <col min="28" max="28" width="31.140625" customWidth="1"/>
-    <col min="29" max="29" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="255.7109375" customWidth="1"/>
+    <col min="19" max="19" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.5" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="23.5" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="17" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="26.5" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="22.33203125" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="15.33203125" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="22.5" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="31.1640625" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="255.6640625" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="36" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.33203125" customWidth="1"/>
+    <col min="34" max="34" width="10.83203125" customWidth="1"/>
+    <col min="36" max="36" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3174,8 +3213,14 @@
       <c r="AF1" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="AG1" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>707</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3272,8 +3317,16 @@
       <c r="AF2">
         <v>1</v>
       </c>
+      <c r="AG2">
+        <f>COUNTIF($AF$2:$AF$300,AF2)</f>
+        <v>1</v>
+      </c>
+      <c r="AH2" t="str">
+        <f>IF(AG2&gt;1,AF2,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="3" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3370,8 +3423,16 @@
       <c r="AF3">
         <v>2</v>
       </c>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG66" si="0">COUNTIF($AF$2:$AF$300,AF3)</f>
+        <v>1</v>
+      </c>
+      <c r="AH3" t="str">
+        <f>IF(AG3&gt;1,AF3,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="4" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3468,8 +3529,16 @@
       <c r="AF4">
         <v>3</v>
       </c>
+      <c r="AG4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH4" t="str">
+        <f>IF(AG4&gt;1,AF4,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="5" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3566,8 +3635,16 @@
       <c r="AF5">
         <v>4</v>
       </c>
+      <c r="AG5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH5" t="str">
+        <f>IF(AG5&gt;1,AF5,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="6" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3664,8 +3741,16 @@
       <c r="AF6">
         <v>5</v>
       </c>
+      <c r="AG6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH6" t="str">
+        <f>IF(AG6&gt;1,AF6,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="7" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3762,8 +3847,19 @@
       <c r="AF7">
         <v>6</v>
       </c>
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH7">
+        <f>IF(AG7&gt;1,AF7,"")</f>
+        <v>6</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3860,8 +3956,16 @@
       <c r="AF8">
         <v>6</v>
       </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH8">
+        <f>IF(AG8&gt;1,AF8,"")</f>
+        <v>6</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3958,8 +4062,19 @@
       <c r="AF9">
         <v>7</v>
       </c>
+      <c r="AG9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH9">
+        <f>IF(AG9&gt;1,AF9,"")</f>
+        <v>7</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4056,8 +4171,16 @@
       <c r="AF10">
         <v>7</v>
       </c>
+      <c r="AG10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH10">
+        <f>IF(AG10&gt;1,AF10,"")</f>
+        <v>7</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4154,8 +4277,19 @@
       <c r="AF11">
         <v>8</v>
       </c>
+      <c r="AG11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH11">
+        <f>IF(AG11&gt;1,AF11,"")</f>
+        <v>8</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4252,8 +4386,16 @@
       <c r="AF12">
         <v>8</v>
       </c>
+      <c r="AG12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH12">
+        <f>IF(AG12&gt;1,AF12,"")</f>
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4350,8 +4492,19 @@
       <c r="AF13">
         <v>9</v>
       </c>
+      <c r="AG13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH13">
+        <f>IF(AG13&gt;1,AF13,"")</f>
+        <v>9</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4448,8 +4601,16 @@
       <c r="AF14">
         <v>9</v>
       </c>
+      <c r="AG14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH14">
+        <f>IF(AG14&gt;1,AF14,"")</f>
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4546,8 +4707,19 @@
       <c r="AF15">
         <v>10</v>
       </c>
+      <c r="AG15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH15">
+        <f>IF(AG15&gt;1,AF15,"")</f>
+        <v>10</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4644,8 +4816,16 @@
       <c r="AF16">
         <v>10</v>
       </c>
+      <c r="AG16">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH16">
+        <f>IF(AG16&gt;1,AF16,"")</f>
+        <v>10</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4742,8 +4922,16 @@
       <c r="AF17">
         <v>11</v>
       </c>
+      <c r="AG17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH17" t="str">
+        <f>IF(AG17&gt;1,AF17,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="18" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4840,8 +5028,16 @@
       <c r="AF18">
         <v>12</v>
       </c>
+      <c r="AG18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH18" t="str">
+        <f>IF(AG18&gt;1,AF18,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4938,8 +5134,16 @@
       <c r="AF19">
         <v>13</v>
       </c>
+      <c r="AG19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH19" t="str">
+        <f>IF(AG19&gt;1,AF19,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5036,8 +5240,16 @@
       <c r="AF20">
         <v>14</v>
       </c>
+      <c r="AG20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH20" t="str">
+        <f>IF(AG20&gt;1,AF20,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="21" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5134,8 +5346,16 @@
       <c r="AF21">
         <v>15</v>
       </c>
+      <c r="AG21">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH21" t="str">
+        <f>IF(AG21&gt;1,AF21,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="22" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5232,8 +5452,16 @@
       <c r="AF22">
         <v>16</v>
       </c>
+      <c r="AG22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH22" t="str">
+        <f>IF(AG22&gt;1,AF22,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="23" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5330,8 +5558,16 @@
       <c r="AF23">
         <v>17</v>
       </c>
+      <c r="AG23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH23" t="str">
+        <f>IF(AG23&gt;1,AF23,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5428,8 +5664,16 @@
       <c r="AF24">
         <v>18</v>
       </c>
+      <c r="AG24">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH24" t="str">
+        <f>IF(AG24&gt;1,AF24,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5526,8 +5770,16 @@
       <c r="AF25">
         <v>19</v>
       </c>
+      <c r="AG25">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH25" t="str">
+        <f>IF(AG25&gt;1,AF25,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="26" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5624,8 +5876,16 @@
       <c r="AF26">
         <v>20</v>
       </c>
+      <c r="AG26">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH26" t="str">
+        <f>IF(AG26&gt;1,AF26,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="27" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5722,8 +5982,16 @@
       <c r="AF27">
         <v>21</v>
       </c>
+      <c r="AG27">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH27" t="str">
+        <f>IF(AG27&gt;1,AF27,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5820,8 +6088,16 @@
       <c r="AF28">
         <v>22</v>
       </c>
+      <c r="AG28">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH28" t="str">
+        <f>IF(AG28&gt;1,AF28,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="29" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5918,8 +6194,16 @@
       <c r="AF29">
         <v>23</v>
       </c>
+      <c r="AG29">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH29" t="str">
+        <f>IF(AG29&gt;1,AF29,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="30" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6016,8 +6300,16 @@
       <c r="AF30">
         <v>24</v>
       </c>
+      <c r="AG30">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH30" t="str">
+        <f>IF(AG30&gt;1,AF30,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="31" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6114,8 +6406,16 @@
       <c r="AF31">
         <v>25</v>
       </c>
+      <c r="AG31">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH31" t="str">
+        <f>IF(AG31&gt;1,AF31,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6212,8 +6512,19 @@
       <c r="AF32">
         <v>26</v>
       </c>
+      <c r="AG32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH32">
+        <f>IF(AG32&gt;1,AF32,"")</f>
+        <v>26</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6310,8 +6621,16 @@
       <c r="AF33">
         <v>26</v>
       </c>
+      <c r="AG33">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH33">
+        <f>IF(AG33&gt;1,AF33,"")</f>
+        <v>26</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6408,8 +6727,19 @@
       <c r="AF34">
         <v>27</v>
       </c>
+      <c r="AG34">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH34">
+        <f>IF(AG34&gt;1,AF34,"")</f>
+        <v>27</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6506,8 +6836,16 @@
       <c r="AF35">
         <v>27</v>
       </c>
+      <c r="AG35">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH35">
+        <f>IF(AG35&gt;1,AF35,"")</f>
+        <v>27</v>
+      </c>
     </row>
-    <row r="36" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6604,8 +6942,16 @@
       <c r="AF36">
         <v>28</v>
       </c>
+      <c r="AG36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH36" t="str">
+        <f>IF(AG36&gt;1,AF36,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="37" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6702,8 +7048,19 @@
       <c r="AF37">
         <v>29</v>
       </c>
+      <c r="AG37">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH37">
+        <f>IF(AG37&gt;1,AF37,"")</f>
+        <v>29</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="38" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6800,8 +7157,16 @@
       <c r="AF38">
         <v>29</v>
       </c>
+      <c r="AG38">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH38">
+        <f>IF(AG38&gt;1,AF38,"")</f>
+        <v>29</v>
+      </c>
     </row>
-    <row r="39" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6898,8 +7263,19 @@
       <c r="AF39">
         <v>30</v>
       </c>
+      <c r="AG39">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH39">
+        <f>IF(AG39&gt;1,AF39,"")</f>
+        <v>30</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="40" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6996,8 +7372,16 @@
       <c r="AF40">
         <v>30</v>
       </c>
+      <c r="AG40">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH40">
+        <f>IF(AG40&gt;1,AF40,"")</f>
+        <v>30</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -7094,8 +7478,16 @@
       <c r="AF41">
         <v>30</v>
       </c>
+      <c r="AG41">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH41">
+        <f>IF(AG41&gt;1,AF41,"")</f>
+        <v>30</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -7192,8 +7584,16 @@
       <c r="AF42">
         <v>30</v>
       </c>
+      <c r="AG42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="AH42">
+        <f>IF(AG42&gt;1,AF42,"")</f>
+        <v>30</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -7290,8 +7690,16 @@
       <c r="AF43">
         <v>31</v>
       </c>
+      <c r="AG43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH43" t="str">
+        <f>IF(AG43&gt;1,AF43,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="44" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7388,8 +7796,16 @@
       <c r="AF44">
         <v>32</v>
       </c>
+      <c r="AG44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH44" t="str">
+        <f>IF(AG44&gt;1,AF44,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="45" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7486,8 +7902,16 @@
       <c r="AF45">
         <v>33</v>
       </c>
+      <c r="AG45">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH45" t="str">
+        <f>IF(AG45&gt;1,AF45,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="46" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7584,8 +8008,16 @@
       <c r="AF46">
         <v>34</v>
       </c>
+      <c r="AG46">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH46" t="str">
+        <f>IF(AG46&gt;1,AF46,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="47" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7682,8 +8114,16 @@
       <c r="AF47">
         <v>35</v>
       </c>
+      <c r="AG47">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH47" t="str">
+        <f>IF(AG47&gt;1,AF47,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="48" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7780,8 +8220,16 @@
       <c r="AF48">
         <v>36</v>
       </c>
+      <c r="AG48">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH48" t="str">
+        <f>IF(AG48&gt;1,AF48,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="49" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7878,8 +8326,16 @@
       <c r="AF49">
         <v>37</v>
       </c>
+      <c r="AG49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH49" t="str">
+        <f>IF(AG49&gt;1,AF49,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="50" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7976,8 +8432,16 @@
       <c r="AF50">
         <v>38</v>
       </c>
+      <c r="AG50">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH50" t="str">
+        <f>IF(AG50&gt;1,AF50,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="51" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8074,8 +8538,16 @@
       <c r="AF51">
         <v>39</v>
       </c>
+      <c r="AG51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH51" t="str">
+        <f>IF(AG51&gt;1,AF51,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="52" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8172,8 +8644,16 @@
       <c r="AF52">
         <v>40</v>
       </c>
+      <c r="AG52">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH52" t="str">
+        <f>IF(AG52&gt;1,AF52,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="53" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8270,8 +8750,16 @@
       <c r="AF53">
         <v>41</v>
       </c>
+      <c r="AG53">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH53" t="str">
+        <f>IF(AG53&gt;1,AF53,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="54" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -8368,8 +8856,16 @@
       <c r="AF54">
         <v>42</v>
       </c>
+      <c r="AG54">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH54" t="str">
+        <f>IF(AG54&gt;1,AF54,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="55" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -8466,8 +8962,16 @@
       <c r="AF55">
         <v>43</v>
       </c>
+      <c r="AG55">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH55" t="str">
+        <f>IF(AG55&gt;1,AF55,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="56" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -8564,8 +9068,16 @@
       <c r="AF56">
         <v>44</v>
       </c>
+      <c r="AG56">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH56" t="str">
+        <f>IF(AG56&gt;1,AF56,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="57" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -8662,8 +9174,16 @@
       <c r="AF57">
         <v>45</v>
       </c>
+      <c r="AG57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH57" t="str">
+        <f>IF(AG57&gt;1,AF57,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="58" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -8760,8 +9280,16 @@
       <c r="AF58">
         <v>46</v>
       </c>
+      <c r="AG58">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH58" t="str">
+        <f>IF(AG58&gt;1,AF58,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="59" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -8858,8 +9386,16 @@
       <c r="AF59">
         <v>47</v>
       </c>
+      <c r="AG59">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH59" t="str">
+        <f>IF(AG59&gt;1,AF59,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="60" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -8956,8 +9492,16 @@
       <c r="AF60">
         <v>48</v>
       </c>
+      <c r="AG60">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH60" t="str">
+        <f>IF(AG60&gt;1,AF60,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="61" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9054,8 +9598,16 @@
       <c r="AF61">
         <v>49</v>
       </c>
+      <c r="AG61">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH61" t="str">
+        <f>IF(AG61&gt;1,AF61,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="62" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9152,8 +9704,16 @@
       <c r="AF62">
         <v>50</v>
       </c>
+      <c r="AG62">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH62" t="str">
+        <f>IF(AG62&gt;1,AF62,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="63" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9250,8 +9810,16 @@
       <c r="AF63">
         <v>51</v>
       </c>
+      <c r="AG63">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH63" t="str">
+        <f>IF(AG63&gt;1,AF63,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="64" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9348,8 +9916,16 @@
       <c r="AF64">
         <v>52</v>
       </c>
+      <c r="AG64">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AH64" t="str">
+        <f>IF(AG64&gt;1,AF64,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="65" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9446,8 +10022,19 @@
       <c r="AF65">
         <v>53</v>
       </c>
+      <c r="AG65">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH65">
+        <f>IF(AG65&gt;1,AF65,"")</f>
+        <v>53</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="66" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9544,8 +10131,16 @@
       <c r="AF66">
         <v>53</v>
       </c>
+      <c r="AG66">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH66">
+        <f>IF(AG66&gt;1,AF66,"")</f>
+        <v>53</v>
+      </c>
     </row>
-    <row r="67" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9642,8 +10237,19 @@
       <c r="AF67">
         <v>54</v>
       </c>
+      <c r="AG67">
+        <f t="shared" ref="AG67:AG130" si="1">COUNTIF($AF$2:$AF$300,AF67)</f>
+        <v>2</v>
+      </c>
+      <c r="AH67">
+        <f>IF(AG67&gt;1,AF67,"")</f>
+        <v>54</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="68" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9740,8 +10346,16 @@
       <c r="AF68">
         <v>54</v>
       </c>
+      <c r="AG68">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH68">
+        <f>IF(AG68&gt;1,AF68,"")</f>
+        <v>54</v>
+      </c>
     </row>
-    <row r="69" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9838,8 +10452,19 @@
       <c r="AF69">
         <v>55</v>
       </c>
+      <c r="AG69">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH69">
+        <f>IF(AG69&gt;1,AF69,"")</f>
+        <v>55</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="70" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9936,8 +10561,16 @@
       <c r="AF70">
         <v>55</v>
       </c>
+      <c r="AG70">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH70">
+        <f>IF(AG70&gt;1,AF70,"")</f>
+        <v>55</v>
+      </c>
     </row>
-    <row r="71" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -10034,8 +10667,19 @@
       <c r="AF71">
         <v>56</v>
       </c>
+      <c r="AG71">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH71">
+        <f>IF(AG71&gt;1,AF71,"")</f>
+        <v>56</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="72" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -10132,8 +10776,16 @@
       <c r="AF72">
         <v>56</v>
       </c>
+      <c r="AG72">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH72">
+        <f>IF(AG72&gt;1,AF72,"")</f>
+        <v>56</v>
+      </c>
     </row>
-    <row r="73" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -10230,8 +10882,16 @@
       <c r="AF73">
         <v>57</v>
       </c>
+      <c r="AG73">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH73" t="str">
+        <f>IF(AG73&gt;1,AF73,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="74" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -10328,8 +10988,16 @@
       <c r="AF74">
         <v>58</v>
       </c>
+      <c r="AG74">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH74" t="str">
+        <f>IF(AG74&gt;1,AF74,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="75" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -10426,8 +11094,16 @@
       <c r="AF75">
         <v>59</v>
       </c>
+      <c r="AG75">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH75" t="str">
+        <f>IF(AG75&gt;1,AF75,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="76" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -10524,8 +11200,16 @@
       <c r="AF76">
         <v>60</v>
       </c>
+      <c r="AG76">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH76" t="str">
+        <f>IF(AG76&gt;1,AF76,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="77" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -10622,8 +11306,16 @@
       <c r="AF77">
         <v>61</v>
       </c>
+      <c r="AG77">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH77" t="str">
+        <f>IF(AG77&gt;1,AF77,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="78" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -10720,8 +11412,16 @@
       <c r="AF78">
         <v>62</v>
       </c>
+      <c r="AG78">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH78" t="str">
+        <f>IF(AG78&gt;1,AF78,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="79" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -10818,8 +11518,16 @@
       <c r="AF79">
         <v>63</v>
       </c>
+      <c r="AG79">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH79" t="str">
+        <f>IF(AG79&gt;1,AF79,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="80" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -10916,8 +11624,19 @@
       <c r="AF80">
         <v>64</v>
       </c>
+      <c r="AG80">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH80">
+        <f>IF(AG80&gt;1,AF80,"")</f>
+        <v>64</v>
+      </c>
+      <c r="AI80" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="81" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -11014,8 +11733,16 @@
       <c r="AF81">
         <v>64</v>
       </c>
+      <c r="AG81">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH81">
+        <f>IF(AG81&gt;1,AF81,"")</f>
+        <v>64</v>
+      </c>
     </row>
-    <row r="82" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -11112,8 +11839,19 @@
       <c r="AF82">
         <v>65</v>
       </c>
+      <c r="AG82">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH82">
+        <f>IF(AG82&gt;1,AF82,"")</f>
+        <v>65</v>
+      </c>
+      <c r="AI82" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="83" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11210,8 +11948,16 @@
       <c r="AF83">
         <v>65</v>
       </c>
+      <c r="AG83">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH83">
+        <f>IF(AG83&gt;1,AF83,"")</f>
+        <v>65</v>
+      </c>
     </row>
-    <row r="84" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -11308,8 +12054,19 @@
       <c r="AF84">
         <v>66</v>
       </c>
+      <c r="AG84">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH84">
+        <f>IF(AG84&gt;1,AF84,"")</f>
+        <v>66</v>
+      </c>
+      <c r="AI84" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="85" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11406,8 +12163,16 @@
       <c r="AF85">
         <v>66</v>
       </c>
+      <c r="AG85">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH85">
+        <f>IF(AG85&gt;1,AF85,"")</f>
+        <v>66</v>
+      </c>
     </row>
-    <row r="86" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -11504,8 +12269,19 @@
       <c r="AF86">
         <v>67</v>
       </c>
+      <c r="AG86">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH86">
+        <f>IF(AG86&gt;1,AF86,"")</f>
+        <v>67</v>
+      </c>
+      <c r="AI86" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="87" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -11602,8 +12378,16 @@
       <c r="AF87">
         <v>67</v>
       </c>
+      <c r="AG87">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH87">
+        <f>IF(AG87&gt;1,AF87,"")</f>
+        <v>67</v>
+      </c>
     </row>
-    <row r="88" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -11700,8 +12484,16 @@
       <c r="AF88">
         <v>68</v>
       </c>
+      <c r="AG88">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH88" t="str">
+        <f>IF(AG88&gt;1,AF88,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="89" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -11798,8 +12590,16 @@
       <c r="AF89">
         <v>69</v>
       </c>
+      <c r="AG89">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH89" t="str">
+        <f>IF(AG89&gt;1,AF89,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="90" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -11896,8 +12696,16 @@
       <c r="AF90">
         <v>70</v>
       </c>
+      <c r="AG90">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH90" t="str">
+        <f>IF(AG90&gt;1,AF90,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="91" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -11994,8 +12802,16 @@
       <c r="AF91">
         <v>71</v>
       </c>
+      <c r="AG91">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH91" t="str">
+        <f>IF(AG91&gt;1,AF91,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="92" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -12092,8 +12908,16 @@
       <c r="AF92">
         <v>72</v>
       </c>
+      <c r="AG92">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH92" t="str">
+        <f>IF(AG92&gt;1,AF92,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="93" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12190,8 +13014,16 @@
       <c r="AF93">
         <v>73</v>
       </c>
+      <c r="AG93">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH93" t="str">
+        <f>IF(AG93&gt;1,AF93,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="94" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -12288,8 +13120,16 @@
       <c r="AF94">
         <v>74</v>
       </c>
+      <c r="AG94">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH94" t="str">
+        <f>IF(AG94&gt;1,AF94,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="95" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12386,8 +13226,16 @@
       <c r="AF95">
         <v>75</v>
       </c>
+      <c r="AG95">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH95" t="str">
+        <f>IF(AG95&gt;1,AF95,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="96" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -12484,8 +13332,16 @@
       <c r="AF96">
         <v>76</v>
       </c>
+      <c r="AG96">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH96" t="str">
+        <f>IF(AG96&gt;1,AF96,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="97" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12582,8 +13438,19 @@
       <c r="AF97">
         <v>77</v>
       </c>
+      <c r="AG97">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH97">
+        <f>IF(AG97&gt;1,AF97,"")</f>
+        <v>77</v>
+      </c>
+      <c r="AI97" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="98" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -12680,8 +13547,16 @@
       <c r="AF98">
         <v>77</v>
       </c>
+      <c r="AG98">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH98">
+        <f>IF(AG98&gt;1,AF98,"")</f>
+        <v>77</v>
+      </c>
     </row>
-    <row r="99" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12778,8 +13653,16 @@
       <c r="AF99">
         <v>77</v>
       </c>
+      <c r="AG99">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH99">
+        <f>IF(AG99&gt;1,AF99,"")</f>
+        <v>77</v>
+      </c>
     </row>
-    <row r="100" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -12876,8 +13759,16 @@
       <c r="AF100">
         <v>77</v>
       </c>
+      <c r="AG100">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH100">
+        <f>IF(AG100&gt;1,AF100,"")</f>
+        <v>77</v>
+      </c>
     </row>
-    <row r="101" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -12974,8 +13865,19 @@
       <c r="AF101">
         <v>78</v>
       </c>
+      <c r="AG101">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH101">
+        <f>IF(AG101&gt;1,AF101,"")</f>
+        <v>78</v>
+      </c>
+      <c r="AI101" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="102" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -13072,8 +13974,16 @@
       <c r="AF102">
         <v>78</v>
       </c>
+      <c r="AG102">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH102">
+        <f>IF(AG102&gt;1,AF102,"")</f>
+        <v>78</v>
+      </c>
     </row>
-    <row r="103" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -13170,8 +14080,16 @@
       <c r="AF103">
         <v>78</v>
       </c>
+      <c r="AG103">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH103">
+        <f>IF(AG103&gt;1,AF103,"")</f>
+        <v>78</v>
+      </c>
     </row>
-    <row r="104" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -13268,8 +14186,16 @@
       <c r="AF104">
         <v>78</v>
       </c>
+      <c r="AG104">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH104">
+        <f>IF(AG104&gt;1,AF104,"")</f>
+        <v>78</v>
+      </c>
     </row>
-    <row r="105" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -13366,8 +14292,16 @@
       <c r="AF105">
         <v>79</v>
       </c>
+      <c r="AG105">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH105" t="str">
+        <f>IF(AG105&gt;1,AF105,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="106" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -13464,8 +14398,19 @@
       <c r="AF106">
         <v>80</v>
       </c>
+      <c r="AG106">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH106">
+        <f>IF(AG106&gt;1,AF106,"")</f>
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="107" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -13562,8 +14507,16 @@
       <c r="AF107">
         <v>80</v>
       </c>
+      <c r="AG107">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH107">
+        <f>IF(AG107&gt;1,AF107,"")</f>
+        <v>80</v>
+      </c>
     </row>
-    <row r="108" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -13660,8 +14613,19 @@
       <c r="AF108">
         <v>81</v>
       </c>
+      <c r="AG108">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH108">
+        <f>IF(AG108&gt;1,AF108,"")</f>
+        <v>81</v>
+      </c>
+      <c r="AI108" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="109" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13758,8 +14722,16 @@
       <c r="AF109">
         <v>81</v>
       </c>
+      <c r="AG109">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH109">
+        <f>IF(AG109&gt;1,AF109,"")</f>
+        <v>81</v>
+      </c>
     </row>
-    <row r="110" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -13856,8 +14828,16 @@
       <c r="AF110">
         <v>81</v>
       </c>
+      <c r="AG110">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH110">
+        <f>IF(AG110&gt;1,AF110,"")</f>
+        <v>81</v>
+      </c>
     </row>
-    <row r="111" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13954,8 +14934,16 @@
       <c r="AF111">
         <v>81</v>
       </c>
+      <c r="AG111">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH111">
+        <f>IF(AG111&gt;1,AF111,"")</f>
+        <v>81</v>
+      </c>
     </row>
-    <row r="112" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -14052,8 +15040,16 @@
       <c r="AF112">
         <v>82</v>
       </c>
+      <c r="AG112">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH112" t="str">
+        <f>IF(AG112&gt;1,AF112,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="113" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -14150,8 +15146,19 @@
       <c r="AF113">
         <v>83</v>
       </c>
+      <c r="AG113">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH113">
+        <f>IF(AG113&gt;1,AF113,"")</f>
+        <v>83</v>
+      </c>
+      <c r="AI113" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="114" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -14248,8 +15255,16 @@
       <c r="AF114">
         <v>83</v>
       </c>
+      <c r="AG114">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH114">
+        <f>IF(AG114&gt;1,AF114,"")</f>
+        <v>83</v>
+      </c>
     </row>
-    <row r="115" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -14346,8 +15361,19 @@
       <c r="AF115">
         <v>84</v>
       </c>
+      <c r="AG115">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH115">
+        <f>IF(AG115&gt;1,AF115,"")</f>
+        <v>84</v>
+      </c>
+      <c r="AI115" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="116" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -14444,8 +15470,16 @@
       <c r="AF116">
         <v>84</v>
       </c>
+      <c r="AG116">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="AH116">
+        <f>IF(AG116&gt;1,AF116,"")</f>
+        <v>84</v>
+      </c>
     </row>
-    <row r="117" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -14542,8 +15576,19 @@
       <c r="AF117">
         <v>85</v>
       </c>
+      <c r="AG117">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH117">
+        <f>IF(AG117&gt;1,AF117,"")</f>
+        <v>85</v>
+      </c>
+      <c r="AI117" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="118" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -14640,8 +15685,16 @@
       <c r="AF118">
         <v>85</v>
       </c>
+      <c r="AG118">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH118">
+        <f>IF(AG118&gt;1,AF118,"")</f>
+        <v>85</v>
+      </c>
     </row>
-    <row r="119" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -14738,8 +15791,16 @@
       <c r="AF119">
         <v>85</v>
       </c>
+      <c r="AG119">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH119">
+        <f>IF(AG119&gt;1,AF119,"")</f>
+        <v>85</v>
+      </c>
     </row>
-    <row r="120" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -14836,8 +15897,16 @@
       <c r="AF120">
         <v>85</v>
       </c>
+      <c r="AG120">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH120">
+        <f>IF(AG120&gt;1,AF120,"")</f>
+        <v>85</v>
+      </c>
     </row>
-    <row r="121" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -14934,8 +16003,19 @@
       <c r="AF121">
         <v>86</v>
       </c>
+      <c r="AG121">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH121">
+        <f>IF(AG121&gt;1,AF121,"")</f>
+        <v>86</v>
+      </c>
+      <c r="AI121" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="122" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -15032,8 +16112,16 @@
       <c r="AF122">
         <v>86</v>
       </c>
+      <c r="AG122">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH122">
+        <f>IF(AG122&gt;1,AF122,"")</f>
+        <v>86</v>
+      </c>
     </row>
-    <row r="123" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -15130,8 +16218,16 @@
       <c r="AF123">
         <v>86</v>
       </c>
+      <c r="AG123">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH123">
+        <f>IF(AG123&gt;1,AF123,"")</f>
+        <v>86</v>
+      </c>
     </row>
-    <row r="124" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -15228,8 +16324,16 @@
       <c r="AF124">
         <v>86</v>
       </c>
+      <c r="AG124">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH124">
+        <f>IF(AG124&gt;1,AF124,"")</f>
+        <v>86</v>
+      </c>
     </row>
-    <row r="125" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -15326,8 +16430,19 @@
       <c r="AF125">
         <v>87</v>
       </c>
+      <c r="AG125">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH125">
+        <f>IF(AG125&gt;1,AF125,"")</f>
+        <v>87</v>
+      </c>
+      <c r="AI125" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="126" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -15424,8 +16539,16 @@
       <c r="AF126">
         <v>87</v>
       </c>
+      <c r="AG126">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH126">
+        <f>IF(AG126&gt;1,AF126,"")</f>
+        <v>87</v>
+      </c>
     </row>
-    <row r="127" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -15522,8 +16645,16 @@
       <c r="AF127">
         <v>87</v>
       </c>
+      <c r="AG127">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH127">
+        <f>IF(AG127&gt;1,AF127,"")</f>
+        <v>87</v>
+      </c>
     </row>
-    <row r="128" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -15620,8 +16751,16 @@
       <c r="AF128">
         <v>87</v>
       </c>
+      <c r="AG128">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AH128">
+        <f>IF(AG128&gt;1,AF128,"")</f>
+        <v>87</v>
+      </c>
     </row>
-    <row r="129" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -15718,8 +16857,19 @@
       <c r="AF129">
         <v>88</v>
       </c>
+      <c r="AG129">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="AH129">
+        <f>IF(AG129&gt;1,AF129,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI129" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="130" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -15816,8 +16966,19 @@
       <c r="AF130">
         <v>88</v>
       </c>
+      <c r="AG130">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="AH130">
+        <f>IF(AG130&gt;1,AF130,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI130" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="131" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -15914,8 +17075,19 @@
       <c r="AF131">
         <v>88</v>
       </c>
+      <c r="AG131">
+        <f t="shared" ref="AG131:AG194" si="2">COUNTIF($AF$2:$AF$300,AF131)</f>
+        <v>12</v>
+      </c>
+      <c r="AH131">
+        <f>IF(AG131&gt;1,AF131,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI131" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="132" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -16012,8 +17184,19 @@
       <c r="AF132">
         <v>88</v>
       </c>
+      <c r="AG132">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH132">
+        <f>IF(AG132&gt;1,AF132,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI132" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="133" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -16110,8 +17293,19 @@
       <c r="AF133">
         <v>88</v>
       </c>
+      <c r="AG133">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH133">
+        <f>IF(AG133&gt;1,AF133,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI133" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="134" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -16208,8 +17402,19 @@
       <c r="AF134">
         <v>88</v>
       </c>
+      <c r="AG134">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH134">
+        <f>IF(AG134&gt;1,AF134,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI134" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="135" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -16306,8 +17511,19 @@
       <c r="AF135">
         <v>88</v>
       </c>
+      <c r="AG135">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH135">
+        <f>IF(AG135&gt;1,AF135,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI135" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="136" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -16404,8 +17620,19 @@
       <c r="AF136">
         <v>88</v>
       </c>
+      <c r="AG136">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH136">
+        <f>IF(AG136&gt;1,AF136,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI136" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="137" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -16502,8 +17729,19 @@
       <c r="AF137">
         <v>88</v>
       </c>
+      <c r="AG137">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH137">
+        <f>IF(AG137&gt;1,AF137,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI137" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="138" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -16600,8 +17838,19 @@
       <c r="AF138">
         <v>88</v>
       </c>
+      <c r="AG138">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH138">
+        <f>IF(AG138&gt;1,AF138,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI138" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="139" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -16698,8 +17947,19 @@
       <c r="AF139">
         <v>88</v>
       </c>
+      <c r="AG139">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH139">
+        <f>IF(AG139&gt;1,AF139,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI139" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="140" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -16796,8 +18056,19 @@
       <c r="AF140">
         <v>88</v>
       </c>
+      <c r="AG140">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH140">
+        <f>IF(AG140&gt;1,AF140,"")</f>
+        <v>88</v>
+      </c>
+      <c r="AI140" t="s">
+        <v>709</v>
+      </c>
     </row>
-    <row r="141" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -16894,8 +18165,19 @@
       <c r="AF141">
         <v>89</v>
       </c>
+      <c r="AG141">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH141">
+        <f>IF(AG141&gt;1,AF141,"")</f>
+        <v>89</v>
+      </c>
+      <c r="AI141" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="142" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -16992,8 +18274,16 @@
       <c r="AF142">
         <v>89</v>
       </c>
+      <c r="AG142">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH142">
+        <f>IF(AG142&gt;1,AF142,"")</f>
+        <v>89</v>
+      </c>
     </row>
-    <row r="143" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -17090,8 +18380,16 @@
       <c r="AF143">
         <v>89</v>
       </c>
+      <c r="AG143">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH143">
+        <f>IF(AG143&gt;1,AF143,"")</f>
+        <v>89</v>
+      </c>
     </row>
-    <row r="144" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -17188,8 +18486,16 @@
       <c r="AF144">
         <v>89</v>
       </c>
+      <c r="AG144">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH144">
+        <f>IF(AG144&gt;1,AF144,"")</f>
+        <v>89</v>
+      </c>
     </row>
-    <row r="145" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -17286,8 +18592,19 @@
       <c r="AF145">
         <v>90</v>
       </c>
+      <c r="AG145">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH145">
+        <f>IF(AG145&gt;1,AF145,"")</f>
+        <v>90</v>
+      </c>
+      <c r="AI145" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="146" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -17384,8 +18701,16 @@
       <c r="AF146">
         <v>90</v>
       </c>
+      <c r="AG146">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH146">
+        <f>IF(AG146&gt;1,AF146,"")</f>
+        <v>90</v>
+      </c>
     </row>
-    <row r="147" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -17482,8 +18807,16 @@
       <c r="AF147">
         <v>90</v>
       </c>
+      <c r="AG147">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH147">
+        <f>IF(AG147&gt;1,AF147,"")</f>
+        <v>90</v>
+      </c>
     </row>
-    <row r="148" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -17580,8 +18913,16 @@
       <c r="AF148">
         <v>90</v>
       </c>
+      <c r="AG148">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH148">
+        <f>IF(AG148&gt;1,AF148,"")</f>
+        <v>90</v>
+      </c>
     </row>
-    <row r="149" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -17678,8 +19019,19 @@
       <c r="AF149">
         <v>91</v>
       </c>
+      <c r="AG149">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH149">
+        <f>IF(AG149&gt;1,AF149,"")</f>
+        <v>91</v>
+      </c>
+      <c r="AI149" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="150" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -17776,8 +19128,16 @@
       <c r="AF150">
         <v>91</v>
       </c>
+      <c r="AG150">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH150">
+        <f>IF(AG150&gt;1,AF150,"")</f>
+        <v>91</v>
+      </c>
     </row>
-    <row r="151" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -17874,8 +19234,16 @@
       <c r="AF151">
         <v>91</v>
       </c>
+      <c r="AG151">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH151">
+        <f>IF(AG151&gt;1,AF151,"")</f>
+        <v>91</v>
+      </c>
     </row>
-    <row r="152" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -17972,8 +19340,16 @@
       <c r="AF152">
         <v>91</v>
       </c>
+      <c r="AG152">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="AH152">
+        <f>IF(AG152&gt;1,AF152,"")</f>
+        <v>91</v>
+      </c>
     </row>
-    <row r="153" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -18070,8 +19446,16 @@
       <c r="AF153">
         <v>92</v>
       </c>
+      <c r="AG153">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH153" t="str">
+        <f>IF(AG153&gt;1,AF153,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="154" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -18168,8 +19552,16 @@
       <c r="AF154">
         <v>93</v>
       </c>
+      <c r="AG154">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH154" t="str">
+        <f>IF(AG154&gt;1,AF154,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="155" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -18266,8 +19658,16 @@
       <c r="AF155">
         <v>94</v>
       </c>
+      <c r="AG155">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH155" t="str">
+        <f>IF(AG155&gt;1,AF155,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="156" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -18364,8 +19764,16 @@
       <c r="AF156">
         <v>95</v>
       </c>
+      <c r="AG156">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH156" t="str">
+        <f>IF(AG156&gt;1,AF156,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="157" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -18462,8 +19870,19 @@
       <c r="AF157" s="3">
         <v>96</v>
       </c>
+      <c r="AG157">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH157">
+        <f>IF(AG157&gt;1,AF157,"")</f>
+        <v>96</v>
+      </c>
+      <c r="AI157" s="3" t="s">
+        <v>710</v>
+      </c>
     </row>
-    <row r="158" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -18560,8 +19979,16 @@
       <c r="AF158" s="3">
         <v>96</v>
       </c>
+      <c r="AG158">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH158">
+        <f>IF(AG158&gt;1,AF158,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="159" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -18658,8 +20085,16 @@
       <c r="AF159" s="3">
         <v>96</v>
       </c>
+      <c r="AG159">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH159">
+        <f>IF(AG159&gt;1,AF159,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="160" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -18756,8 +20191,16 @@
       <c r="AF160" s="3">
         <v>96</v>
       </c>
+      <c r="AG160">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH160">
+        <f>IF(AG160&gt;1,AF160,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="161" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -18854,8 +20297,16 @@
       <c r="AF161" s="3">
         <v>96</v>
       </c>
+      <c r="AG161">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH161">
+        <f>IF(AG161&gt;1,AF161,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="162" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -18952,8 +20403,16 @@
       <c r="AF162" s="3">
         <v>96</v>
       </c>
+      <c r="AG162">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH162">
+        <f>IF(AG162&gt;1,AF162,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="163" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -19050,8 +20509,16 @@
       <c r="AF163" s="3">
         <v>96</v>
       </c>
+      <c r="AG163">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH163">
+        <f>IF(AG163&gt;1,AF163,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="164" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -19148,8 +20615,16 @@
       <c r="AF164" s="3">
         <v>96</v>
       </c>
+      <c r="AG164">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH164">
+        <f>IF(AG164&gt;1,AF164,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="165" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -19246,8 +20721,16 @@
       <c r="AF165" s="3">
         <v>96</v>
       </c>
+      <c r="AG165">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH165">
+        <f>IF(AG165&gt;1,AF165,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="166" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -19344,8 +20827,16 @@
       <c r="AF166" s="3">
         <v>96</v>
       </c>
+      <c r="AG166">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH166">
+        <f>IF(AG166&gt;1,AF166,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="167" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -19442,8 +20933,16 @@
       <c r="AF167" s="3">
         <v>96</v>
       </c>
+      <c r="AG167">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH167">
+        <f>IF(AG167&gt;1,AF167,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="168" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -19540,8 +21039,16 @@
       <c r="AF168" s="3">
         <v>96</v>
       </c>
+      <c r="AG168">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="AH168">
+        <f>IF(AG168&gt;1,AF168,"")</f>
+        <v>96</v>
+      </c>
     </row>
-    <row r="169" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -19638,8 +21145,16 @@
       <c r="AF169">
         <v>97</v>
       </c>
+      <c r="AG169">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH169" t="str">
+        <f>IF(AG169&gt;1,AF169,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="170" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -19736,8 +21251,16 @@
       <c r="AF170">
         <v>98</v>
       </c>
+      <c r="AG170">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH170" t="str">
+        <f>IF(AG170&gt;1,AF170,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="171" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -19834,8 +21357,16 @@
       <c r="AF171">
         <v>99</v>
       </c>
+      <c r="AG171">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH171" t="str">
+        <f>IF(AG171&gt;1,AF171,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="172" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -19932,8 +21463,16 @@
       <c r="AF172">
         <v>100</v>
       </c>
+      <c r="AG172">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH172" t="str">
+        <f>IF(AG172&gt;1,AF172,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="173" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -20030,8 +21569,16 @@
       <c r="AF173">
         <v>101</v>
       </c>
+      <c r="AG173">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH173" t="str">
+        <f>IF(AG173&gt;1,AF173,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="174" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -20128,8 +21675,16 @@
       <c r="AF174">
         <v>102</v>
       </c>
+      <c r="AG174">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH174" t="str">
+        <f>IF(AG174&gt;1,AF174,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="175" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -20226,8 +21781,16 @@
       <c r="AF175">
         <v>103</v>
       </c>
+      <c r="AG175">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH175" t="str">
+        <f>IF(AG175&gt;1,AF175,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="176" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -20324,8 +21887,16 @@
       <c r="AF176">
         <v>104</v>
       </c>
+      <c r="AG176">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH176" t="str">
+        <f>IF(AG176&gt;1,AF176,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="177" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -20422,8 +21993,16 @@
       <c r="AF177">
         <v>105</v>
       </c>
+      <c r="AG177">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH177" t="str">
+        <f>IF(AG177&gt;1,AF177,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="178" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -20520,8 +22099,16 @@
       <c r="AF178">
         <v>106</v>
       </c>
+      <c r="AG178">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH178" t="str">
+        <f>IF(AG178&gt;1,AF178,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="179" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
@@ -20618,8 +22205,16 @@
       <c r="AF179">
         <v>107</v>
       </c>
+      <c r="AG179">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH179" t="str">
+        <f>IF(AG179&gt;1,AF179,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="180" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
@@ -20716,8 +22311,16 @@
       <c r="AF180">
         <v>108</v>
       </c>
+      <c r="AG180">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH180" t="str">
+        <f>IF(AG180&gt;1,AF180,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="181" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -20814,8 +22417,16 @@
       <c r="AF181">
         <v>109</v>
       </c>
+      <c r="AG181">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH181" t="str">
+        <f>IF(AG181&gt;1,AF181,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="182" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>181</v>
       </c>
@@ -20912,8 +22523,16 @@
       <c r="AF182">
         <v>110</v>
       </c>
+      <c r="AG182">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH182" t="str">
+        <f>IF(AG182&gt;1,AF182,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="183" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>182</v>
       </c>
@@ -21010,8 +22629,16 @@
       <c r="AF183">
         <v>111</v>
       </c>
+      <c r="AG183">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH183" t="str">
+        <f>IF(AG183&gt;1,AF183,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="184" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>183</v>
       </c>
@@ -21108,8 +22735,16 @@
       <c r="AF184">
         <v>112</v>
       </c>
+      <c r="AG184">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH184" t="str">
+        <f>IF(AG184&gt;1,AF184,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="185" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -21206,8 +22841,16 @@
       <c r="AF185">
         <v>113</v>
       </c>
+      <c r="AG185">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH185" t="str">
+        <f>IF(AG185&gt;1,AF185,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="186" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>185</v>
       </c>
@@ -21304,8 +22947,19 @@
       <c r="AF186">
         <v>114</v>
       </c>
+      <c r="AG186">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AH186">
+        <f>IF(AG186&gt;1,AF186,"")</f>
+        <v>114</v>
+      </c>
+      <c r="AI186" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="187" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>186</v>
       </c>
@@ -21402,8 +23056,16 @@
       <c r="AF187">
         <v>114</v>
       </c>
+      <c r="AG187">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AH187">
+        <f>IF(AG187&gt;1,AF187,"")</f>
+        <v>114</v>
+      </c>
     </row>
-    <row r="188" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>187</v>
       </c>
@@ -21500,8 +23162,19 @@
       <c r="AF188">
         <v>115</v>
       </c>
+      <c r="AG188">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AH188">
+        <f>IF(AG188&gt;1,AF188,"")</f>
+        <v>115</v>
+      </c>
+      <c r="AI188" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="189" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>188</v>
       </c>
@@ -21598,8 +23271,16 @@
       <c r="AF189">
         <v>115</v>
       </c>
+      <c r="AG189">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="AH189">
+        <f>IF(AG189&gt;1,AF189,"")</f>
+        <v>115</v>
+      </c>
     </row>
-    <row r="190" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>189</v>
       </c>
@@ -21696,8 +23377,16 @@
       <c r="AF190">
         <v>116</v>
       </c>
+      <c r="AG190">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH190" t="str">
+        <f>IF(AG190&gt;1,AF190,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="191" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>190</v>
       </c>
@@ -21794,8 +23483,16 @@
       <c r="AF191">
         <v>117</v>
       </c>
+      <c r="AG191">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH191" t="str">
+        <f>IF(AG191&gt;1,AF191,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="192" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>191</v>
       </c>
@@ -21892,8 +23589,16 @@
       <c r="AF192">
         <v>118</v>
       </c>
+      <c r="AG192">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH192" t="str">
+        <f>IF(AG192&gt;1,AF192,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="193" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -21990,8 +23695,16 @@
       <c r="AF193">
         <v>119</v>
       </c>
+      <c r="AG193">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH193" t="str">
+        <f>IF(AG193&gt;1,AF193,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="194" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -22088,8 +23801,16 @@
       <c r="AF194">
         <v>120</v>
       </c>
+      <c r="AG194">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AH194" t="str">
+        <f>IF(AG194&gt;1,AF194,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="195" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -22186,8 +23907,16 @@
       <c r="AF195">
         <v>121</v>
       </c>
+      <c r="AG195">
+        <f t="shared" ref="AG195:AG258" si="3">COUNTIF($AF$2:$AF$300,AF195)</f>
+        <v>1</v>
+      </c>
+      <c r="AH195" t="str">
+        <f>IF(AG195&gt;1,AF195,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="196" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -22284,8 +24013,16 @@
       <c r="AF196">
         <v>122</v>
       </c>
+      <c r="AG196">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH196" t="str">
+        <f>IF(AG196&gt;1,AF196,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="197" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -22382,8 +24119,16 @@
       <c r="AF197">
         <v>123</v>
       </c>
+      <c r="AG197">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH197" t="str">
+        <f>IF(AG197&gt;1,AF197,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="198" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -22480,8 +24225,16 @@
       <c r="AF198">
         <v>124</v>
       </c>
+      <c r="AG198">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH198" t="str">
+        <f>IF(AG198&gt;1,AF198,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="199" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -22578,8 +24331,16 @@
       <c r="AF199">
         <v>125</v>
       </c>
+      <c r="AG199">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH199" t="str">
+        <f>IF(AG199&gt;1,AF199,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="200" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -22676,8 +24437,19 @@
       <c r="AF200">
         <v>126</v>
       </c>
+      <c r="AG200">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH200">
+        <f>IF(AG200&gt;1,AF200,"")</f>
+        <v>126</v>
+      </c>
+      <c r="AI200" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="201" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -22774,8 +24546,16 @@
       <c r="AF201">
         <v>126</v>
       </c>
+      <c r="AG201">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH201">
+        <f>IF(AG201&gt;1,AF201,"")</f>
+        <v>126</v>
+      </c>
     </row>
-    <row r="202" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -22872,8 +24652,19 @@
       <c r="AF202">
         <v>127</v>
       </c>
+      <c r="AG202">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH202">
+        <f>IF(AG202&gt;1,AF202,"")</f>
+        <v>127</v>
+      </c>
+      <c r="AI202" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="203" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
@@ -22970,8 +24761,16 @@
       <c r="AF203">
         <v>127</v>
       </c>
+      <c r="AG203">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH203">
+        <f>IF(AG203&gt;1,AF203,"")</f>
+        <v>127</v>
+      </c>
     </row>
-    <row r="204" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -23068,8 +24867,19 @@
       <c r="AF204">
         <v>128</v>
       </c>
+      <c r="AG204">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH204">
+        <f>IF(AG204&gt;1,AF204,"")</f>
+        <v>128</v>
+      </c>
+      <c r="AI204" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="205" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -23166,8 +24976,16 @@
       <c r="AF205">
         <v>128</v>
       </c>
+      <c r="AG205">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="AH205">
+        <f>IF(AG205&gt;1,AF205,"")</f>
+        <v>128</v>
+      </c>
     </row>
-    <row r="206" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -23264,8 +25082,16 @@
       <c r="AF206">
         <v>129</v>
       </c>
+      <c r="AG206">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH206" t="str">
+        <f>IF(AG206&gt;1,AF206,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="207" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -23362,8 +25188,16 @@
       <c r="AF207">
         <v>130</v>
       </c>
+      <c r="AG207">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH207" t="str">
+        <f>IF(AG207&gt;1,AF207,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="208" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -23460,8 +25294,16 @@
       <c r="AF208">
         <v>131</v>
       </c>
+      <c r="AG208">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH208" t="str">
+        <f>IF(AG208&gt;1,AF208,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="209" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -23558,8 +25400,16 @@
       <c r="AF209">
         <v>132</v>
       </c>
+      <c r="AG209">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH209" t="str">
+        <f>IF(AG209&gt;1,AF209,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="210" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -23656,8 +25506,16 @@
       <c r="AF210">
         <v>133</v>
       </c>
+      <c r="AG210">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH210" t="str">
+        <f>IF(AG210&gt;1,AF210,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="211" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -23754,8 +25612,16 @@
       <c r="AF211">
         <v>134</v>
       </c>
+      <c r="AG211">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH211" t="str">
+        <f>IF(AG211&gt;1,AF211,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="212" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -23852,8 +25718,16 @@
       <c r="AF212">
         <v>135</v>
       </c>
+      <c r="AG212">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH212" t="str">
+        <f>IF(AG212&gt;1,AF212,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="213" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -23950,8 +25824,16 @@
       <c r="AF213">
         <v>136</v>
       </c>
+      <c r="AG213">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH213" t="str">
+        <f>IF(AG213&gt;1,AF213,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="214" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -24048,8 +25930,16 @@
       <c r="AF214">
         <v>137</v>
       </c>
+      <c r="AG214">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH214" t="str">
+        <f>IF(AG214&gt;1,AF214,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="215" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
@@ -24146,8 +26036,16 @@
       <c r="AF215">
         <v>138</v>
       </c>
+      <c r="AG215">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH215" t="str">
+        <f>IF(AG215&gt;1,AF215,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="216" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
@@ -24244,8 +26142,16 @@
       <c r="AF216">
         <v>139</v>
       </c>
+      <c r="AG216">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH216" t="str">
+        <f>IF(AG216&gt;1,AF216,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="217" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
@@ -24342,8 +26248,16 @@
       <c r="AF217">
         <v>140</v>
       </c>
+      <c r="AG217">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH217" t="str">
+        <f>IF(AG217&gt;1,AF217,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="218" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
@@ -24440,8 +26354,16 @@
       <c r="AF218">
         <v>141</v>
       </c>
+      <c r="AG218">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH218" t="str">
+        <f>IF(AG218&gt;1,AF218,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="219" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
@@ -24538,8 +26460,16 @@
       <c r="AF219">
         <v>142</v>
       </c>
+      <c r="AG219">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH219" t="str">
+        <f>IF(AG219&gt;1,AF219,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="220" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
@@ -24636,8 +26566,16 @@
       <c r="AF220">
         <v>143</v>
       </c>
+      <c r="AG220">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH220" t="str">
+        <f>IF(AG220&gt;1,AF220,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="221" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
@@ -24734,8 +26672,19 @@
       <c r="AF221">
         <v>144</v>
       </c>
+      <c r="AG221">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH221">
+        <f>IF(AG221&gt;1,AF221,"")</f>
+        <v>144</v>
+      </c>
+      <c r="AI221" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="222" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
@@ -24832,8 +26781,16 @@
       <c r="AF222">
         <v>144</v>
       </c>
+      <c r="AG222">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH222">
+        <f>IF(AG222&gt;1,AF222,"")</f>
+        <v>144</v>
+      </c>
     </row>
-    <row r="223" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
@@ -24930,8 +26887,16 @@
       <c r="AF223">
         <v>144</v>
       </c>
+      <c r="AG223">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH223">
+        <f>IF(AG223&gt;1,AF223,"")</f>
+        <v>144</v>
+      </c>
     </row>
-    <row r="224" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>223</v>
       </c>
@@ -25028,8 +26993,16 @@
       <c r="AF224">
         <v>144</v>
       </c>
+      <c r="AG224">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH224">
+        <f>IF(AG224&gt;1,AF224,"")</f>
+        <v>144</v>
+      </c>
     </row>
-    <row r="225" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>224</v>
       </c>
@@ -25126,8 +27099,19 @@
       <c r="AF225">
         <v>145</v>
       </c>
+      <c r="AG225">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH225">
+        <f>IF(AG225&gt;1,AF225,"")</f>
+        <v>145</v>
+      </c>
+      <c r="AI225" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="226" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>225</v>
       </c>
@@ -25224,8 +27208,16 @@
       <c r="AF226">
         <v>145</v>
       </c>
+      <c r="AG226">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH226">
+        <f>IF(AG226&gt;1,AF226,"")</f>
+        <v>145</v>
+      </c>
     </row>
-    <row r="227" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>226</v>
       </c>
@@ -25322,8 +27314,16 @@
       <c r="AF227">
         <v>145</v>
       </c>
+      <c r="AG227">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH227">
+        <f>IF(AG227&gt;1,AF227,"")</f>
+        <v>145</v>
+      </c>
     </row>
-    <row r="228" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>227</v>
       </c>
@@ -25420,8 +27420,16 @@
       <c r="AF228">
         <v>145</v>
       </c>
+      <c r="AG228">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH228">
+        <f>IF(AG228&gt;1,AF228,"")</f>
+        <v>145</v>
+      </c>
     </row>
-    <row r="229" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>228</v>
       </c>
@@ -25518,8 +27526,19 @@
       <c r="AF229">
         <v>146</v>
       </c>
+      <c r="AG229">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH229">
+        <f>IF(AG229&gt;1,AF229,"")</f>
+        <v>146</v>
+      </c>
+      <c r="AI229" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="230" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>229</v>
       </c>
@@ -25616,8 +27635,16 @@
       <c r="AF230">
         <v>146</v>
       </c>
+      <c r="AG230">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH230">
+        <f>IF(AG230&gt;1,AF230,"")</f>
+        <v>146</v>
+      </c>
     </row>
-    <row r="231" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>230</v>
       </c>
@@ -25714,8 +27741,16 @@
       <c r="AF231">
         <v>146</v>
       </c>
+      <c r="AG231">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH231">
+        <f>IF(AG231&gt;1,AF231,"")</f>
+        <v>146</v>
+      </c>
     </row>
-    <row r="232" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>231</v>
       </c>
@@ -25812,8 +27847,16 @@
       <c r="AF232">
         <v>146</v>
       </c>
+      <c r="AG232">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH232">
+        <f>IF(AG232&gt;1,AF232,"")</f>
+        <v>146</v>
+      </c>
     </row>
-    <row r="233" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>232</v>
       </c>
@@ -25910,8 +27953,19 @@
       <c r="AF233">
         <v>147</v>
       </c>
+      <c r="AG233">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH233">
+        <f>IF(AG233&gt;1,AF233,"")</f>
+        <v>147</v>
+      </c>
+      <c r="AI233" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="234" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>233</v>
       </c>
@@ -26008,8 +28062,16 @@
       <c r="AF234">
         <v>147</v>
       </c>
+      <c r="AG234">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH234">
+        <f>IF(AG234&gt;1,AF234,"")</f>
+        <v>147</v>
+      </c>
     </row>
-    <row r="235" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>234</v>
       </c>
@@ -26106,8 +28168,16 @@
       <c r="AF235">
         <v>147</v>
       </c>
+      <c r="AG235">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH235">
+        <f>IF(AG235&gt;1,AF235,"")</f>
+        <v>147</v>
+      </c>
     </row>
-    <row r="236" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>235</v>
       </c>
@@ -26204,8 +28274,16 @@
       <c r="AF236">
         <v>147</v>
       </c>
+      <c r="AG236">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="AH236">
+        <f>IF(AG236&gt;1,AF236,"")</f>
+        <v>147</v>
+      </c>
     </row>
-    <row r="237" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>236</v>
       </c>
@@ -26302,8 +28380,16 @@
       <c r="AF237">
         <v>148</v>
       </c>
+      <c r="AG237">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH237" t="str">
+        <f>IF(AG237&gt;1,AF237,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="238" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>237</v>
       </c>
@@ -26400,8 +28486,16 @@
       <c r="AF238">
         <v>149</v>
       </c>
+      <c r="AG238">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH238" t="str">
+        <f>IF(AG238&gt;1,AF238,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="239" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>238</v>
       </c>
@@ -26498,8 +28592,16 @@
       <c r="AF239">
         <v>150</v>
       </c>
+      <c r="AG239">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH239" t="str">
+        <f>IF(AG239&gt;1,AF239,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="240" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>239</v>
       </c>
@@ -26596,8 +28698,16 @@
       <c r="AF240">
         <v>151</v>
       </c>
+      <c r="AG240">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH240" t="str">
+        <f>IF(AG240&gt;1,AF240,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="241" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>240</v>
       </c>
@@ -26694,8 +28804,16 @@
       <c r="AF241">
         <v>152</v>
       </c>
+      <c r="AG241">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH241" t="str">
+        <f>IF(AG241&gt;1,AF241,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="242" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>241</v>
       </c>
@@ -26792,8 +28910,16 @@
       <c r="AF242">
         <v>153</v>
       </c>
+      <c r="AG242">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH242" t="str">
+        <f>IF(AG242&gt;1,AF242,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="243" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>242</v>
       </c>
@@ -26890,8 +29016,16 @@
       <c r="AF243">
         <v>154</v>
       </c>
+      <c r="AG243">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH243" t="str">
+        <f>IF(AG243&gt;1,AF243,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="244" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>243</v>
       </c>
@@ -26988,8 +29122,16 @@
       <c r="AF244">
         <v>155</v>
       </c>
+      <c r="AG244">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH244" t="str">
+        <f>IF(AG244&gt;1,AF244,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="245" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>244</v>
       </c>
@@ -27086,8 +29228,16 @@
       <c r="AF245">
         <v>156</v>
       </c>
+      <c r="AG245">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH245" t="str">
+        <f>IF(AG245&gt;1,AF245,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="246" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -27184,8 +29334,16 @@
       <c r="AF246" s="3">
         <v>157</v>
       </c>
+      <c r="AG246">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH246" t="str">
+        <f>IF(AG246&gt;1,AF246,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="247" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -27282,8 +29440,16 @@
       <c r="AF247" s="3">
         <v>158</v>
       </c>
+      <c r="AG247">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH247" t="str">
+        <f>IF(AG247&gt;1,AF247,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="248" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>247</v>
       </c>
@@ -27380,8 +29546,16 @@
       <c r="AF248" s="3">
         <v>159</v>
       </c>
+      <c r="AG248">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH248" t="str">
+        <f>IF(AG248&gt;1,AF248,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="249" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>248</v>
       </c>
@@ -27478,8 +29652,16 @@
       <c r="AF249" s="3">
         <v>160</v>
       </c>
+      <c r="AG249">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH249" t="str">
+        <f>IF(AG249&gt;1,AF249,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="250" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>249</v>
       </c>
@@ -27576,8 +29758,16 @@
       <c r="AF250" s="3">
         <v>161</v>
       </c>
+      <c r="AG250">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH250" t="str">
+        <f>IF(AG250&gt;1,AF250,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="251" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>250</v>
       </c>
@@ -27674,8 +29864,16 @@
       <c r="AF251" s="3">
         <v>162</v>
       </c>
+      <c r="AG251">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH251" t="str">
+        <f>IF(AG251&gt;1,AF251,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="252" spans="1:32" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:34" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>251</v>
       </c>
@@ -27772,8 +29970,16 @@
       <c r="AF252" s="3">
         <v>163</v>
       </c>
+      <c r="AG252">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH252" t="str">
+        <f>IF(AG252&gt;1,AF252,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="253" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>252</v>
       </c>
@@ -27870,8 +30076,16 @@
       <c r="AF253">
         <v>164</v>
       </c>
+      <c r="AG253">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH253" t="str">
+        <f>IF(AG253&gt;1,AF253,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="254" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>253</v>
       </c>
@@ -27968,8 +30182,16 @@
       <c r="AF254">
         <v>165</v>
       </c>
+      <c r="AG254">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH254" t="str">
+        <f>IF(AG254&gt;1,AF254,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="255" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>254</v>
       </c>
@@ -28066,8 +30288,16 @@
       <c r="AF255">
         <v>166</v>
       </c>
+      <c r="AG255">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH255" t="str">
+        <f>IF(AG255&gt;1,AF255,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="256" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>255</v>
       </c>
@@ -28164,8 +30394,16 @@
       <c r="AF256">
         <v>167</v>
       </c>
+      <c r="AG256">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH256" t="str">
+        <f>IF(AG256&gt;1,AF256,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="257" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>256</v>
       </c>
@@ -28262,8 +30500,16 @@
       <c r="AF257">
         <v>168</v>
       </c>
+      <c r="AG257">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH257" t="str">
+        <f>IF(AG257&gt;1,AF257,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="258" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>257</v>
       </c>
@@ -28360,8 +30606,16 @@
       <c r="AF258">
         <v>169</v>
       </c>
+      <c r="AG258">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="AH258" t="str">
+        <f>IF(AG258&gt;1,AF258,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="259" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>258</v>
       </c>
@@ -28458,8 +30712,16 @@
       <c r="AF259">
         <v>170</v>
       </c>
+      <c r="AG259">
+        <f t="shared" ref="AG259:AG289" si="4">COUNTIF($AF$2:$AF$300,AF259)</f>
+        <v>1</v>
+      </c>
+      <c r="AH259" t="str">
+        <f>IF(AG259&gt;1,AF259,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="260" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>259</v>
       </c>
@@ -28556,8 +30818,16 @@
       <c r="AF260">
         <v>171</v>
       </c>
+      <c r="AG260">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH260" t="str">
+        <f>IF(AG260&gt;1,AF260,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="261" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>260</v>
       </c>
@@ -28654,8 +30924,16 @@
       <c r="AF261">
         <v>172</v>
       </c>
+      <c r="AG261">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH261" t="str">
+        <f>IF(AG261&gt;1,AF261,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="262" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>261</v>
       </c>
@@ -28752,8 +31030,16 @@
       <c r="AF262">
         <v>173</v>
       </c>
+      <c r="AG262">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH262" t="str">
+        <f>IF(AG262&gt;1,AF262,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="263" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>262</v>
       </c>
@@ -28850,8 +31136,16 @@
       <c r="AF263">
         <v>174</v>
       </c>
+      <c r="AG263">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH263" t="str">
+        <f>IF(AG263&gt;1,AF263,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="264" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>263</v>
       </c>
@@ -28948,8 +31242,16 @@
       <c r="AF264">
         <v>175</v>
       </c>
+      <c r="AG264">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH264" t="str">
+        <f>IF(AG264&gt;1,AF264,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="265" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>264</v>
       </c>
@@ -29046,8 +31348,16 @@
       <c r="AF265">
         <v>176</v>
       </c>
+      <c r="AG265">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH265" t="str">
+        <f>IF(AG265&gt;1,AF265,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="266" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>265</v>
       </c>
@@ -29144,8 +31454,16 @@
       <c r="AF266">
         <v>177</v>
       </c>
+      <c r="AG266">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH266" t="str">
+        <f>IF(AG266&gt;1,AF266,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="267" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>266</v>
       </c>
@@ -29242,8 +31560,16 @@
       <c r="AF267">
         <v>178</v>
       </c>
+      <c r="AG267">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH267" t="str">
+        <f>IF(AG267&gt;1,AF267,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="268" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>267</v>
       </c>
@@ -29340,8 +31666,16 @@
       <c r="AF268">
         <v>179</v>
       </c>
+      <c r="AG268">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH268" t="str">
+        <f>IF(AG268&gt;1,AF268,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="269" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>268</v>
       </c>
@@ -29438,8 +31772,19 @@
       <c r="AF269">
         <v>180</v>
       </c>
+      <c r="AG269">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH269">
+        <f>IF(AG269&gt;1,AF269,"")</f>
+        <v>180</v>
+      </c>
+      <c r="AI269" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="270" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>269</v>
       </c>
@@ -29536,8 +31881,16 @@
       <c r="AF270">
         <v>180</v>
       </c>
+      <c r="AG270">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AH270">
+        <f>IF(AG270&gt;1,AF270,"")</f>
+        <v>180</v>
+      </c>
     </row>
-    <row r="271" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>270</v>
       </c>
@@ -29634,8 +31987,16 @@
       <c r="AF271">
         <v>181</v>
       </c>
+      <c r="AG271">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH271" t="str">
+        <f>IF(AG271&gt;1,AF271,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="272" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>271</v>
       </c>
@@ -29732,8 +32093,16 @@
       <c r="AF272">
         <v>182</v>
       </c>
+      <c r="AG272">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH272" t="str">
+        <f>IF(AG272&gt;1,AF272,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="273" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>272</v>
       </c>
@@ -29830,8 +32199,16 @@
       <c r="AF273">
         <v>183</v>
       </c>
+      <c r="AG273">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH273" t="str">
+        <f>IF(AG273&gt;1,AF273,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="274" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>273</v>
       </c>
@@ -29928,8 +32305,16 @@
       <c r="AF274">
         <v>184</v>
       </c>
+      <c r="AG274">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH274" t="str">
+        <f>IF(AG274&gt;1,AF274,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="275" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>274</v>
       </c>
@@ -30026,8 +32411,16 @@
       <c r="AF275">
         <v>185</v>
       </c>
+      <c r="AG275">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH275" t="str">
+        <f>IF(AG275&gt;1,AF275,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="276" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>275</v>
       </c>
@@ -30124,8 +32517,16 @@
       <c r="AF276">
         <v>186</v>
       </c>
+      <c r="AG276">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH276" t="str">
+        <f>IF(AG276&gt;1,AF276,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="277" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>276</v>
       </c>
@@ -30222,8 +32623,16 @@
       <c r="AF277">
         <v>187</v>
       </c>
+      <c r="AG277">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH277" t="str">
+        <f>IF(AG277&gt;1,AF277,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="278" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>277</v>
       </c>
@@ -30320,8 +32729,16 @@
       <c r="AF278">
         <v>188</v>
       </c>
+      <c r="AG278">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH278" t="str">
+        <f>IF(AG278&gt;1,AF278,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="279" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>278</v>
       </c>
@@ -30418,8 +32835,16 @@
       <c r="AF279">
         <v>189</v>
       </c>
+      <c r="AG279">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH279" t="str">
+        <f>IF(AG279&gt;1,AF279,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="280" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>279</v>
       </c>
@@ -30516,8 +32941,16 @@
       <c r="AF280">
         <v>190</v>
       </c>
+      <c r="AG280">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH280" t="str">
+        <f>IF(AG280&gt;1,AF280,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="281" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>280</v>
       </c>
@@ -30614,8 +33047,16 @@
       <c r="AF281">
         <v>191</v>
       </c>
+      <c r="AG281">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH281" t="str">
+        <f>IF(AG281&gt;1,AF281,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="282" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>281</v>
       </c>
@@ -30712,8 +33153,16 @@
       <c r="AF282">
         <v>192</v>
       </c>
+      <c r="AG282">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH282" t="str">
+        <f>IF(AG282&gt;1,AF282,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="283" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>282</v>
       </c>
@@ -30810,8 +33259,19 @@
       <c r="AF283">
         <v>193</v>
       </c>
+      <c r="AG283">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH283">
+        <f>IF(AG283&gt;1,AF283,"")</f>
+        <v>193</v>
+      </c>
+      <c r="AI283" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
-    <row r="284" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>283</v>
       </c>
@@ -30908,8 +33368,16 @@
       <c r="AF284">
         <v>193</v>
       </c>
+      <c r="AG284">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH284">
+        <f>IF(AG284&gt;1,AF284,"")</f>
+        <v>193</v>
+      </c>
     </row>
-    <row r="285" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>284</v>
       </c>
@@ -31006,8 +33474,16 @@
       <c r="AF285">
         <v>193</v>
       </c>
+      <c r="AG285">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH285">
+        <f>IF(AG285&gt;1,AF285,"")</f>
+        <v>193</v>
+      </c>
     </row>
-    <row r="286" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>285</v>
       </c>
@@ -31104,8 +33580,16 @@
       <c r="AF286">
         <v>193</v>
       </c>
+      <c r="AG286">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AH286">
+        <f>IF(AG286&gt;1,AF286,"")</f>
+        <v>193</v>
+      </c>
     </row>
-    <row r="287" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>286</v>
       </c>
@@ -31202,8 +33686,16 @@
       <c r="AF287">
         <v>194</v>
       </c>
+      <c r="AG287">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH287" t="str">
+        <f>IF(AG287&gt;1,AF287,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="288" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>287</v>
       </c>
@@ -31300,8 +33792,16 @@
       <c r="AF288">
         <v>195</v>
       </c>
+      <c r="AG288">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH288" t="str">
+        <f>IF(AG288&gt;1,AF288,"")</f>
+        <v/>
+      </c>
     </row>
-    <row r="289" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
@@ -31397,6 +33897,14 @@
       </c>
       <c r="AF289">
         <v>196</v>
+      </c>
+      <c r="AG289">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH289" t="str">
+        <f>IF(AG289&gt;1,AF289,"")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
